--- a/5 semester/MathProg/lab 3 — копия/ЛР№2ЛашкинВар№17.xlsx
+++ b/5 semester/MathProg/lab 3 — копия/ЛР№2ЛашкинВар№17.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSUIR\COURSE 3\МатПрог\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sasha\BSUIR\5 semester\MathProg\lab 3 — копия\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E077B43B-2E5B-41F7-9AFC-85C7E11297FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2D1890-C72F-4765-91A7-E35AB723DEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Задание 1" sheetId="1" r:id="rId1"/>
@@ -97,6 +97,7 @@
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1758,11 +1759,29 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1770,34 +1789,16 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{466E1C6A-CFDD-494A-8068-6F4078A7D8F5}"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3417,128 +3418,128 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BC504"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="7" width="8.88671875" style="1"/>
-    <col min="8" max="8" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="7" width="8.90625" style="1"/>
+    <col min="8" max="8" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="118" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="118" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="H3" s="123" t="s">
+    <row r="1" spans="1:18" s="116" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="116" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="H3" s="117" t="s">
         <v>245</v>
       </c>
-      <c r="I3" s="123"/>
-      <c r="J3" s="123"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="H4" s="123" t="s">
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="H4" s="117" t="s">
         <v>246</v>
       </c>
-      <c r="I4" s="123"/>
-      <c r="J4" s="123"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="H5" s="123" t="s">
-        <v>0</v>
-      </c>
-      <c r="I5" s="123"/>
-      <c r="J5" s="123"/>
-    </row>
-    <row r="10" spans="1:18" s="118" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="118" t="s">
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="H5" s="117" t="s">
+        <v>0</v>
+      </c>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+    </row>
+    <row r="10" spans="1:18" s="116" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="116" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A15" s="122" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="122"/>
-      <c r="J15" s="122"/>
-      <c r="K15" s="122"/>
-      <c r="L15" s="122"/>
-      <c r="M15" s="122"/>
-      <c r="N15" s="122"/>
-      <c r="O15" s="122"/>
-      <c r="P15" s="122"/>
-      <c r="Q15" s="122"/>
-      <c r="R15" s="122"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A16" s="121" t="s">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A15" s="115" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="115"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="115"/>
+      <c r="K15" s="115"/>
+      <c r="L15" s="115"/>
+      <c r="M15" s="115"/>
+      <c r="N15" s="115"/>
+      <c r="O15" s="115"/>
+      <c r="P15" s="115"/>
+      <c r="Q15" s="115"/>
+      <c r="R15" s="115"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A16" s="114" t="s">
         <v>247</v>
       </c>
-      <c r="B16" s="121"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="121" t="s">
+      <c r="B16" s="114"/>
+      <c r="C16" s="114"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="114" t="s">
         <v>251</v>
       </c>
-      <c r="F16" s="121"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="121"/>
-    </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A17" s="121" t="s">
+      <c r="F16" s="114"/>
+      <c r="G16" s="114"/>
+      <c r="H16" s="114"/>
+    </row>
+    <row r="17" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A17" s="114" t="s">
         <v>248</v>
       </c>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121" t="s">
+      <c r="B17" s="114"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="114"/>
+      <c r="E17" s="114" t="s">
         <v>252</v>
       </c>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-    </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A18" s="121" t="s">
+      <c r="F17" s="114"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="114"/>
+    </row>
+    <row r="18" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A18" s="114" t="s">
         <v>249</v>
       </c>
-      <c r="B18" s="121"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="121" t="s">
+      <c r="B18" s="114"/>
+      <c r="C18" s="114"/>
+      <c r="D18" s="114"/>
+      <c r="E18" s="114" t="s">
         <v>253</v>
       </c>
-      <c r="F18" s="121"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-    </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A19" s="121" t="s">
+      <c r="F18" s="114"/>
+      <c r="G18" s="114"/>
+      <c r="H18" s="114"/>
+    </row>
+    <row r="19" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A19" s="114" t="s">
         <v>250</v>
       </c>
-      <c r="B19" s="121"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121" t="s">
+      <c r="B19" s="114"/>
+      <c r="C19" s="114"/>
+      <c r="D19" s="114"/>
+      <c r="E19" s="114" t="s">
         <v>254</v>
       </c>
-      <c r="F19" s="121"/>
-      <c r="G19" s="121"/>
-      <c r="H19" s="121"/>
-    </row>
-    <row r="20" spans="1:41" s="118" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="118" t="s">
+      <c r="F19" s="114"/>
+      <c r="G19" s="114"/>
+      <c r="H19" s="114"/>
+    </row>
+    <row r="20" spans="1:41" s="116" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="116" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
@@ -3552,13 +3553,13 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.45">
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>4</v>
       </c>
@@ -3568,13 +3569,13 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.45">
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A26" s="22" t="s">
         <v>5</v>
       </c>
@@ -3682,8 +3683,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A27" s="114">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A27" s="118">
         <v>40</v>
       </c>
       <c r="B27" s="8">
@@ -3699,7 +3700,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="114">
+      <c r="G27" s="118">
         <v>0</v>
       </c>
       <c r="H27" s="15">
@@ -3714,7 +3715,7 @@
       <c r="K27" s="13">
         <v>1</v>
       </c>
-      <c r="M27" s="114">
+      <c r="M27" s="118">
         <v>0</v>
       </c>
       <c r="N27" s="15">
@@ -3729,7 +3730,7 @@
       <c r="Q27" s="13">
         <v>1</v>
       </c>
-      <c r="S27" s="114">
+      <c r="S27" s="118">
         <v>0</v>
       </c>
       <c r="T27" s="15">
@@ -3744,7 +3745,7 @@
       <c r="W27" s="13">
         <v>1</v>
       </c>
-      <c r="Y27" s="114">
+      <c r="Y27" s="118">
         <v>0</v>
       </c>
       <c r="Z27" s="15">
@@ -3759,7 +3760,7 @@
       <c r="AC27" s="13">
         <v>1</v>
       </c>
-      <c r="AE27" s="114">
+      <c r="AE27" s="118">
         <v>0</v>
       </c>
       <c r="AF27" s="15">
@@ -3774,7 +3775,7 @@
       <c r="AI27" s="13">
         <v>1</v>
       </c>
-      <c r="AK27" s="114">
+      <c r="AK27" s="118">
         <v>0</v>
       </c>
       <c r="AL27" s="15">
@@ -3790,49 +3791,49 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A28" s="115"/>
+    <row r="28" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A28" s="119"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
       <c r="E28" s="12"/>
       <c r="F28" s="4"/>
-      <c r="G28" s="115"/>
+      <c r="G28" s="119"/>
       <c r="H28" s="16">
         <v>40</v>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14"/>
       <c r="K28" s="14"/>
-      <c r="M28" s="115"/>
+      <c r="M28" s="119"/>
       <c r="N28" s="16">
         <v>40</v>
       </c>
       <c r="O28" s="14"/>
       <c r="P28" s="14"/>
       <c r="Q28" s="14"/>
-      <c r="S28" s="115"/>
+      <c r="S28" s="119"/>
       <c r="T28" s="16">
         <v>40</v>
       </c>
       <c r="U28" s="14"/>
       <c r="V28" s="14"/>
       <c r="W28" s="14"/>
-      <c r="Y28" s="115"/>
+      <c r="Y28" s="119"/>
       <c r="Z28" s="16">
         <v>40</v>
       </c>
       <c r="AA28" s="14"/>
       <c r="AB28" s="14"/>
       <c r="AC28" s="14"/>
-      <c r="AE28" s="115"/>
+      <c r="AE28" s="119"/>
       <c r="AF28" s="16">
         <v>40</v>
       </c>
       <c r="AG28" s="14"/>
       <c r="AH28" s="14"/>
       <c r="AI28" s="14"/>
-      <c r="AK28" s="115"/>
+      <c r="AK28" s="119"/>
       <c r="AL28" s="16">
         <v>40</v>
       </c>
@@ -3840,8 +3841,8 @@
       <c r="AN28" s="14"/>
       <c r="AO28" s="14"/>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A29" s="114">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A29" s="118">
         <v>50</v>
       </c>
       <c r="B29" s="8">
@@ -3857,7 +3858,7 @@
         <v>9</v>
       </c>
       <c r="F29" s="3"/>
-      <c r="G29" s="114">
+      <c r="G29" s="118">
         <v>50</v>
       </c>
       <c r="H29" s="13">
@@ -3873,7 +3874,7 @@
         <v>9</v>
       </c>
       <c r="L29" s="2"/>
-      <c r="M29" s="114">
+      <c r="M29" s="118">
         <v>0</v>
       </c>
       <c r="N29" s="13">
@@ -3888,7 +3889,7 @@
       <c r="Q29" s="13">
         <v>9</v>
       </c>
-      <c r="S29" s="114">
+      <c r="S29" s="118">
         <v>0</v>
       </c>
       <c r="T29" s="13">
@@ -3903,7 +3904,7 @@
       <c r="W29" s="13">
         <v>9</v>
       </c>
-      <c r="Y29" s="114">
+      <c r="Y29" s="118">
         <v>0</v>
       </c>
       <c r="Z29" s="13">
@@ -3918,7 +3919,7 @@
       <c r="AC29" s="13">
         <v>9</v>
       </c>
-      <c r="AE29" s="114">
+      <c r="AE29" s="118">
         <v>0</v>
       </c>
       <c r="AF29" s="13">
@@ -3933,7 +3934,7 @@
       <c r="AI29" s="13">
         <v>9</v>
       </c>
-      <c r="AK29" s="114">
+      <c r="AK29" s="118">
         <v>0</v>
       </c>
       <c r="AL29" s="13">
@@ -3949,48 +3950,48 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A30" s="115"/>
+    <row r="30" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A30" s="119"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
       <c r="E30" s="12"/>
       <c r="F30" s="4"/>
-      <c r="G30" s="115"/>
+      <c r="G30" s="119"/>
       <c r="H30" s="14"/>
       <c r="I30" s="12"/>
       <c r="J30" s="12"/>
       <c r="K30" s="12"/>
       <c r="L30" s="2"/>
-      <c r="M30" s="115"/>
+      <c r="M30" s="119"/>
       <c r="N30" s="14"/>
       <c r="O30" s="16">
         <v>50</v>
       </c>
       <c r="P30" s="14"/>
       <c r="Q30" s="14"/>
-      <c r="S30" s="115"/>
+      <c r="S30" s="119"/>
       <c r="T30" s="14"/>
       <c r="U30" s="16">
         <v>50</v>
       </c>
       <c r="V30" s="14"/>
       <c r="W30" s="14"/>
-      <c r="Y30" s="115"/>
+      <c r="Y30" s="119"/>
       <c r="Z30" s="14"/>
       <c r="AA30" s="16">
         <v>50</v>
       </c>
       <c r="AB30" s="14"/>
       <c r="AC30" s="14"/>
-      <c r="AE30" s="115"/>
+      <c r="AE30" s="119"/>
       <c r="AF30" s="14"/>
       <c r="AG30" s="16">
         <v>50</v>
       </c>
       <c r="AH30" s="14"/>
       <c r="AI30" s="14"/>
-      <c r="AK30" s="115"/>
+      <c r="AK30" s="119"/>
       <c r="AL30" s="14"/>
       <c r="AM30" s="16">
         <v>50</v>
@@ -3998,8 +3999,8 @@
       <c r="AN30" s="14"/>
       <c r="AO30" s="14"/>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A31" s="114">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A31" s="118">
         <v>50</v>
       </c>
       <c r="B31" s="10">
@@ -4015,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F31" s="3"/>
-      <c r="G31" s="114">
+      <c r="G31" s="118">
         <v>50</v>
       </c>
       <c r="H31" s="18">
@@ -4030,7 +4031,7 @@
       <c r="K31" s="10">
         <v>5</v>
       </c>
-      <c r="M31" s="114">
+      <c r="M31" s="118">
         <v>50</v>
       </c>
       <c r="N31" s="18">
@@ -4045,7 +4046,7 @@
       <c r="Q31" s="10">
         <v>5</v>
       </c>
-      <c r="S31" s="114">
+      <c r="S31" s="118">
         <v>10</v>
       </c>
       <c r="T31" s="18">
@@ -4060,7 +4061,7 @@
       <c r="W31" s="17">
         <v>5</v>
       </c>
-      <c r="Y31" s="114">
+      <c r="Y31" s="118">
         <v>0</v>
       </c>
       <c r="Z31" s="18">
@@ -4075,7 +4076,7 @@
       <c r="AC31" s="17">
         <v>5</v>
       </c>
-      <c r="AE31" s="114">
+      <c r="AE31" s="118">
         <v>0</v>
       </c>
       <c r="AF31" s="18">
@@ -4090,7 +4091,7 @@
       <c r="AI31" s="17">
         <v>5</v>
       </c>
-      <c r="AK31" s="114">
+      <c r="AK31" s="118">
         <v>0</v>
       </c>
       <c r="AL31" s="18">
@@ -4106,31 +4107,31 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A32" s="115"/>
+    <row r="32" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A32" s="119"/>
       <c r="B32" s="38"/>
       <c r="C32" s="38"/>
       <c r="D32" s="38"/>
       <c r="E32" s="38"/>
       <c r="F32" s="4"/>
-      <c r="G32" s="115"/>
+      <c r="G32" s="119"/>
       <c r="H32" s="39"/>
       <c r="I32" s="38"/>
       <c r="J32" s="38"/>
       <c r="K32" s="38"/>
-      <c r="M32" s="115"/>
+      <c r="M32" s="119"/>
       <c r="N32" s="39"/>
       <c r="O32" s="38"/>
       <c r="P32" s="38"/>
       <c r="Q32" s="38"/>
-      <c r="S32" s="115"/>
+      <c r="S32" s="119"/>
       <c r="T32" s="39"/>
       <c r="U32" s="38"/>
       <c r="V32" s="38"/>
       <c r="W32" s="40">
         <v>40</v>
       </c>
-      <c r="Y32" s="115"/>
+      <c r="Y32" s="119"/>
       <c r="Z32" s="39"/>
       <c r="AA32" s="40">
         <v>10</v>
@@ -4139,7 +4140,7 @@
       <c r="AC32" s="40">
         <v>40</v>
       </c>
-      <c r="AE32" s="115"/>
+      <c r="AE32" s="119"/>
       <c r="AF32" s="39"/>
       <c r="AG32" s="40">
         <v>10</v>
@@ -4148,7 +4149,7 @@
       <c r="AI32" s="40">
         <v>40</v>
       </c>
-      <c r="AK32" s="115"/>
+      <c r="AK32" s="119"/>
       <c r="AL32" s="39"/>
       <c r="AM32" s="40">
         <v>10</v>
@@ -4158,8 +4159,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A33" s="114">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A33" s="118">
         <v>40</v>
       </c>
       <c r="B33" s="8">
@@ -4175,7 +4176,7 @@
         <v>6</v>
       </c>
       <c r="F33" s="3"/>
-      <c r="G33" s="114">
+      <c r="G33" s="118">
         <v>40</v>
       </c>
       <c r="H33" s="13">
@@ -4190,7 +4191,7 @@
       <c r="K33" s="8">
         <v>6</v>
       </c>
-      <c r="M33" s="114">
+      <c r="M33" s="118">
         <v>40</v>
       </c>
       <c r="N33" s="13">
@@ -4205,7 +4206,7 @@
       <c r="Q33" s="8">
         <v>6</v>
       </c>
-      <c r="S33" s="114">
+      <c r="S33" s="118">
         <v>40</v>
       </c>
       <c r="T33" s="13">
@@ -4220,7 +4221,7 @@
       <c r="W33" s="13">
         <v>6</v>
       </c>
-      <c r="Y33" s="114">
+      <c r="Y33" s="118">
         <v>40</v>
       </c>
       <c r="Z33" s="13">
@@ -4235,7 +4236,7 @@
       <c r="AC33" s="13">
         <v>6</v>
       </c>
-      <c r="AE33" s="114">
+      <c r="AE33" s="118">
         <v>0</v>
       </c>
       <c r="AF33" s="13">
@@ -4250,7 +4251,7 @@
       <c r="AI33" s="13">
         <v>6</v>
       </c>
-      <c r="AK33" s="114">
+      <c r="AK33" s="118">
         <v>0</v>
       </c>
       <c r="AL33" s="13">
@@ -4266,41 +4267,41 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A34" s="115"/>
+    <row r="34" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A34" s="119"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
       <c r="E34" s="12"/>
       <c r="F34" s="4"/>
-      <c r="G34" s="115"/>
+      <c r="G34" s="119"/>
       <c r="H34" s="14"/>
       <c r="I34" s="12"/>
       <c r="J34" s="12"/>
       <c r="K34" s="12"/>
-      <c r="M34" s="115"/>
+      <c r="M34" s="119"/>
       <c r="N34" s="14"/>
       <c r="O34" s="12"/>
       <c r="P34" s="12"/>
       <c r="Q34" s="12"/>
-      <c r="S34" s="115"/>
+      <c r="S34" s="119"/>
       <c r="T34" s="14"/>
       <c r="U34" s="12"/>
       <c r="V34" s="12"/>
       <c r="W34" s="14"/>
-      <c r="Y34" s="115"/>
+      <c r="Y34" s="119"/>
       <c r="Z34" s="14"/>
       <c r="AA34" s="14"/>
       <c r="AB34" s="12"/>
       <c r="AC34" s="14"/>
-      <c r="AE34" s="115"/>
+      <c r="AE34" s="119"/>
       <c r="AF34" s="14"/>
       <c r="AG34" s="14"/>
       <c r="AH34" s="16">
         <v>40</v>
       </c>
       <c r="AI34" s="14"/>
-      <c r="AK34" s="115"/>
+      <c r="AK34" s="119"/>
       <c r="AL34" s="14"/>
       <c r="AM34" s="14"/>
       <c r="AN34" s="16">
@@ -4308,8 +4309,8 @@
       </c>
       <c r="AO34" s="14"/>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A35" s="119">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A35" s="120">
         <v>10</v>
       </c>
       <c r="B35" s="26">
@@ -4325,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="4"/>
-      <c r="G35" s="119">
+      <c r="G35" s="120">
         <v>10</v>
       </c>
       <c r="H35" s="31">
@@ -4340,7 +4341,7 @@
       <c r="K35" s="26">
         <v>0</v>
       </c>
-      <c r="M35" s="119">
+      <c r="M35" s="120">
         <v>10</v>
       </c>
       <c r="N35" s="31">
@@ -4355,7 +4356,7 @@
       <c r="Q35" s="26">
         <v>0</v>
       </c>
-      <c r="S35" s="119">
+      <c r="S35" s="120">
         <v>10</v>
       </c>
       <c r="T35" s="31">
@@ -4370,7 +4371,7 @@
       <c r="W35" s="31">
         <v>0</v>
       </c>
-      <c r="Y35" s="119">
+      <c r="Y35" s="120">
         <v>10</v>
       </c>
       <c r="Z35" s="31">
@@ -4385,7 +4386,7 @@
       <c r="AC35" s="31">
         <v>0</v>
       </c>
-      <c r="AE35" s="119">
+      <c r="AE35" s="120">
         <v>10</v>
       </c>
       <c r="AF35" s="31">
@@ -4400,7 +4401,7 @@
       <c r="AI35" s="31">
         <v>0</v>
       </c>
-      <c r="AK35" s="119">
+      <c r="AK35" s="120">
         <v>0</v>
       </c>
       <c r="AL35" s="31">
@@ -4416,39 +4417,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A36" s="120"/>
+    <row r="36" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A36" s="121"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
       <c r="E36" s="12"/>
       <c r="F36" s="4"/>
-      <c r="G36" s="120"/>
+      <c r="G36" s="121"/>
       <c r="H36" s="14"/>
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
       <c r="K36" s="12"/>
-      <c r="M36" s="120"/>
+      <c r="M36" s="121"/>
       <c r="N36" s="14"/>
       <c r="O36" s="12"/>
       <c r="P36" s="12"/>
       <c r="Q36" s="12"/>
-      <c r="S36" s="120"/>
+      <c r="S36" s="121"/>
       <c r="T36" s="14"/>
       <c r="U36" s="12"/>
       <c r="V36" s="12"/>
       <c r="W36" s="14"/>
-      <c r="Y36" s="120"/>
+      <c r="Y36" s="121"/>
       <c r="Z36" s="14"/>
       <c r="AA36" s="14"/>
       <c r="AB36" s="12"/>
       <c r="AC36" s="14"/>
-      <c r="AE36" s="120"/>
+      <c r="AE36" s="121"/>
       <c r="AF36" s="14"/>
       <c r="AG36" s="14"/>
       <c r="AH36" s="12"/>
       <c r="AI36" s="14"/>
-      <c r="AK36" s="120"/>
+      <c r="AK36" s="121"/>
       <c r="AL36" s="14"/>
       <c r="AM36" s="14"/>
       <c r="AN36" s="16">
@@ -4456,12 +4457,12 @@
       </c>
       <c r="AO36" s="14"/>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A40" s="22" t="s">
         <v>5</v>
       </c>
@@ -4478,8 +4479,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A41" s="114">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A41" s="118">
         <v>0</v>
       </c>
       <c r="B41" s="15">
@@ -4495,8 +4496,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A42" s="115"/>
+    <row r="42" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A42" s="119"/>
       <c r="B42" s="16">
         <v>40</v>
       </c>
@@ -4504,8 +4505,8 @@
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
     </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A43" s="114">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A43" s="118">
         <v>0</v>
       </c>
       <c r="B43" s="13">
@@ -4521,8 +4522,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A44" s="115"/>
+    <row r="44" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A44" s="119"/>
       <c r="B44" s="14"/>
       <c r="C44" s="16">
         <v>50</v>
@@ -4530,8 +4531,8 @@
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
     </row>
-    <row r="45" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A45" s="114">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A45" s="118">
         <v>0</v>
       </c>
       <c r="B45" s="18">
@@ -4547,8 +4548,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A46" s="115"/>
+    <row r="46" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A46" s="119"/>
       <c r="B46" s="39"/>
       <c r="C46" s="40">
         <v>10</v>
@@ -4558,8 +4559,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A47" s="114">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A47" s="118">
         <v>0</v>
       </c>
       <c r="B47" s="13">
@@ -4575,8 +4576,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:41" x14ac:dyDescent="0.4">
-      <c r="A48" s="115"/>
+    <row r="48" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A48" s="119"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="16">
@@ -4584,8 +4585,8 @@
       </c>
       <c r="E48" s="14"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A49" s="119">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A49" s="120">
         <v>0</v>
       </c>
       <c r="B49" s="31">
@@ -4601,8 +4602,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A50" s="120"/>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" s="121"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="16">
@@ -4610,22 +4611,22 @@
       </c>
       <c r="E50" s="14"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" s="22"/>
       <c r="B57" s="23" t="s">
         <v>19</v>
@@ -4643,7 +4644,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" s="34" t="s">
         <v>23</v>
       </c>
@@ -4663,7 +4664,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" s="35"/>
       <c r="B59" s="16">
         <v>40</v>
@@ -4681,7 +4682,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" s="34" t="s">
         <v>24</v>
       </c>
@@ -4701,7 +4702,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" s="35"/>
       <c r="B61" s="14" t="s">
         <v>30</v>
@@ -4719,7 +4720,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" s="34" t="s">
         <v>25</v>
       </c>
@@ -4739,7 +4740,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" s="35"/>
       <c r="B63" s="14" t="s">
         <v>29</v>
@@ -4757,7 +4758,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" s="34" t="s">
         <v>26</v>
       </c>
@@ -4777,7 +4778,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" s="35"/>
       <c r="B65" s="14" t="s">
         <v>33</v>
@@ -4792,7 +4793,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="36" t="s">
         <v>27</v>
       </c>
@@ -4809,7 +4810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" s="37"/>
       <c r="B67" s="14" t="s">
         <v>34</v>
@@ -4824,12 +4825,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69" s="42" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="22"/>
       <c r="B71" s="23" t="s">
         <v>19</v>
@@ -4844,7 +4845,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="34" t="s">
         <v>23</v>
       </c>
@@ -4861,7 +4862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="35"/>
       <c r="B73" s="16" t="s">
         <v>39</v>
@@ -4876,7 +4877,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="34" t="s">
         <v>24</v>
       </c>
@@ -4893,7 +4894,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="35"/>
       <c r="B75" s="14" t="s">
         <v>30</v>
@@ -4908,7 +4909,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="34" t="s">
         <v>25</v>
       </c>
@@ -4925,7 +4926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="35"/>
       <c r="B77" s="14" t="s">
         <v>29</v>
@@ -4940,7 +4941,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="34" t="s">
         <v>26</v>
       </c>
@@ -4957,7 +4958,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="35"/>
       <c r="B79" s="14" t="s">
         <v>38</v>
@@ -4972,7 +4973,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="36" t="s">
         <v>27</v>
       </c>
@@ -4989,7 +4990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" s="37"/>
       <c r="B81" s="14" t="s">
         <v>34</v>
@@ -5007,12 +5008,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85" s="22" t="s">
         <v>5</v>
       </c>
@@ -5029,8 +5030,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A86" s="114">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A86" s="118">
         <v>0</v>
       </c>
       <c r="B86" s="13">
@@ -5046,8 +5047,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A87" s="115"/>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A87" s="119"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
       <c r="D87" s="14"/>
@@ -5055,8 +5056,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A88" s="114">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A88" s="118">
         <v>0</v>
       </c>
       <c r="B88" s="13">
@@ -5072,8 +5073,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A89" s="115"/>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A89" s="119"/>
       <c r="B89" s="14"/>
       <c r="C89" s="16">
         <v>10</v>
@@ -5083,8 +5084,8 @@
       </c>
       <c r="E89" s="14"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A90" s="114">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A90" s="118">
         <v>0</v>
       </c>
       <c r="B90" s="18">
@@ -5100,8 +5101,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A91" s="115"/>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A91" s="119"/>
       <c r="B91" s="39"/>
       <c r="C91" s="40">
         <v>50</v>
@@ -5111,8 +5112,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A92" s="114">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A92" s="118">
         <v>0</v>
       </c>
       <c r="B92" s="15">
@@ -5128,8 +5129,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A93" s="115"/>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A93" s="119"/>
       <c r="B93" s="16">
         <v>40</v>
       </c>
@@ -5139,8 +5140,8 @@
       </c>
       <c r="E93" s="14"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A94" s="119">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A94" s="120">
         <v>0</v>
       </c>
       <c r="B94" s="31">
@@ -5156,8 +5157,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A95" s="120"/>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A95" s="121"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
       <c r="D95" s="16">
@@ -5165,12 +5166,12 @@
       </c>
       <c r="E95" s="14"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" s="22"/>
       <c r="B99" s="23" t="s">
         <v>44</v>
@@ -5188,7 +5189,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" s="34" t="s">
         <v>23</v>
       </c>
@@ -5208,7 +5209,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101" s="35"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14" t="s">
@@ -5222,7 +5223,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" s="34" t="s">
         <v>24</v>
       </c>
@@ -5242,7 +5243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" s="35"/>
       <c r="B103" s="14"/>
       <c r="C103" s="16">
@@ -5256,7 +5257,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" s="34" t="s">
         <v>25</v>
       </c>
@@ -5276,7 +5277,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" s="35"/>
       <c r="B105" s="39"/>
       <c r="C105" s="40">
@@ -5290,7 +5291,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" s="34" t="s">
         <v>26</v>
       </c>
@@ -5310,7 +5311,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" s="35"/>
       <c r="B107" s="16">
         <v>40</v>
@@ -5323,7 +5324,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108" s="36" t="s">
         <v>27</v>
       </c>
@@ -5340,7 +5341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109" s="37"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
@@ -5349,12 +5350,12 @@
       </c>
       <c r="E109" s="14"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" s="42" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" s="22"/>
       <c r="B113" s="23" t="s">
         <v>44</v>
@@ -5369,7 +5370,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114" s="34" t="s">
         <v>23</v>
       </c>
@@ -5386,7 +5387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" s="35"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14" t="s">
@@ -5397,7 +5398,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" s="34" t="s">
         <v>24</v>
       </c>
@@ -5414,7 +5415,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117" s="35"/>
       <c r="B117" s="14"/>
       <c r="C117" s="16" t="s">
@@ -5425,7 +5426,7 @@
       </c>
       <c r="E117" s="14"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" s="34" t="s">
         <v>25</v>
       </c>
@@ -5442,7 +5443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" s="35"/>
       <c r="B119" s="39"/>
       <c r="C119" s="40" t="s">
@@ -5453,7 +5454,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" s="34" t="s">
         <v>26</v>
       </c>
@@ -5470,7 +5471,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" s="35"/>
       <c r="B121" s="16">
         <v>40</v>
@@ -5483,7 +5484,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A122" s="36" t="s">
         <v>27</v>
       </c>
@@ -5500,7 +5501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123" s="37"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
@@ -5512,12 +5513,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A127" s="22" t="s">
         <v>5</v>
       </c>
@@ -5534,8 +5535,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A128" s="114">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A128" s="118">
         <v>0</v>
       </c>
       <c r="B128" s="13">
@@ -5551,8 +5552,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A129" s="115"/>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A129" s="119"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
       <c r="D129" s="14"/>
@@ -5560,8 +5561,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A130" s="114">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A130" s="118">
         <v>0</v>
       </c>
       <c r="B130" s="13">
@@ -5577,8 +5578,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A131" s="115"/>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A131" s="119"/>
       <c r="B131" s="14"/>
       <c r="C131" s="16">
         <v>10</v>
@@ -5588,8 +5589,8 @@
       </c>
       <c r="E131" s="14"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A132" s="114">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A132" s="118">
         <v>0</v>
       </c>
       <c r="B132" s="18">
@@ -5605,8 +5606,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A133" s="115"/>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A133" s="119"/>
       <c r="B133" s="39"/>
       <c r="C133" s="40">
         <v>50</v>
@@ -5614,8 +5615,8 @@
       <c r="D133" s="39"/>
       <c r="E133" s="39"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A134" s="114">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A134" s="118">
         <v>0</v>
       </c>
       <c r="B134" s="15">
@@ -5631,8 +5632,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A135" s="115"/>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A135" s="119"/>
       <c r="B135" s="16">
         <v>40</v>
       </c>
@@ -5644,8 +5645,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A136" s="119">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A136" s="120">
         <v>0</v>
       </c>
       <c r="B136" s="31">
@@ -5661,8 +5662,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A137" s="120"/>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A137" s="121"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
       <c r="D137" s="16">
@@ -5670,12 +5671,12 @@
       </c>
       <c r="E137" s="14"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141" s="22"/>
       <c r="B141" s="23" t="s">
         <v>53</v>
@@ -5693,8 +5694,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A142" s="114" t="s">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A142" s="118" t="s">
         <v>23</v>
       </c>
       <c r="B142" s="13">
@@ -5713,8 +5714,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A143" s="115"/>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A143" s="119"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14" t="s">
         <v>68</v>
@@ -5729,8 +5730,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A144" s="114" t="s">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A144" s="118" t="s">
         <v>56</v>
       </c>
       <c r="B144" s="13">
@@ -5749,8 +5750,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A145" s="115"/>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A145" s="119"/>
       <c r="B145" s="14"/>
       <c r="C145" s="16">
         <v>10</v>
@@ -5763,8 +5764,8 @@
         <v>63</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A146" s="114" t="s">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A146" s="118" t="s">
         <v>57</v>
       </c>
       <c r="B146" s="18">
@@ -5783,8 +5784,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A147" s="115"/>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A147" s="119"/>
       <c r="B147" s="39"/>
       <c r="C147" s="40">
         <v>50</v>
@@ -5797,8 +5798,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A148" s="114" t="s">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A148" s="118" t="s">
         <v>58</v>
       </c>
       <c r="B148" s="15">
@@ -5817,8 +5818,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A149" s="115"/>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A149" s="119"/>
       <c r="B149" s="16">
         <v>40</v>
       </c>
@@ -5830,8 +5831,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A150" s="119" t="s">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A150" s="120" t="s">
         <v>59</v>
       </c>
       <c r="B150" s="31">
@@ -5847,8 +5848,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A151" s="120"/>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A151" s="121"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
       <c r="D151" s="16">
@@ -5856,12 +5857,12 @@
       </c>
       <c r="E151" s="14"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A153" s="42" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A155" s="22"/>
       <c r="B155" s="23" t="s">
         <v>53</v>
@@ -5876,8 +5877,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A156" s="114" t="s">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A156" s="118" t="s">
         <v>23</v>
       </c>
       <c r="B156" s="13">
@@ -5893,8 +5894,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A157" s="115"/>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A157" s="119"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14" t="s">
         <v>69</v>
@@ -5906,8 +5907,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A158" s="114" t="s">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A158" s="118" t="s">
         <v>56</v>
       </c>
       <c r="B158" s="13">
@@ -5923,8 +5924,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A159" s="115"/>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A159" s="119"/>
       <c r="B159" s="14"/>
       <c r="C159" s="16" t="s">
         <v>49</v>
@@ -5934,8 +5935,8 @@
       </c>
       <c r="E159" s="14"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A160" s="114" t="s">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A160" s="118" t="s">
         <v>57</v>
       </c>
       <c r="B160" s="18">
@@ -5951,8 +5952,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A161" s="115"/>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A161" s="119"/>
       <c r="B161" s="39"/>
       <c r="C161" s="40">
         <v>50</v>
@@ -5962,8 +5963,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A162" s="114" t="s">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A162" s="118" t="s">
         <v>58</v>
       </c>
       <c r="B162" s="15">
@@ -5979,8 +5980,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A163" s="115"/>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A163" s="119"/>
       <c r="B163" s="16">
         <v>40</v>
       </c>
@@ -5992,8 +5993,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A164" s="119" t="s">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A164" s="120" t="s">
         <v>59</v>
       </c>
       <c r="B164" s="31">
@@ -6009,8 +6010,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A165" s="120"/>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A165" s="121"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
       <c r="D165" s="16">
@@ -6021,12 +6022,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A169" s="22" t="s">
         <v>5</v>
       </c>
@@ -6043,8 +6044,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A170" s="114">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A170" s="118">
         <v>0</v>
       </c>
       <c r="B170" s="13">
@@ -6060,8 +6061,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A171" s="115"/>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A171" s="119"/>
       <c r="B171" s="14"/>
       <c r="C171" s="16">
         <v>0</v>
@@ -6071,8 +6072,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A172" s="114">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A172" s="118">
         <v>0</v>
       </c>
       <c r="B172" s="13">
@@ -6088,8 +6089,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A173" s="115"/>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A173" s="119"/>
       <c r="B173" s="14"/>
       <c r="C173" s="16">
         <v>10</v>
@@ -6099,8 +6100,8 @@
       </c>
       <c r="E173" s="14"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A174" s="114">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A174" s="118">
         <v>0</v>
       </c>
       <c r="B174" s="18">
@@ -6116,8 +6117,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A175" s="115"/>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A175" s="119"/>
       <c r="B175" s="39"/>
       <c r="C175" s="40">
         <v>50</v>
@@ -6125,8 +6126,8 @@
       <c r="D175" s="39"/>
       <c r="E175" s="39"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A176" s="114">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A176" s="118">
         <v>0</v>
       </c>
       <c r="B176" s="15">
@@ -6142,8 +6143,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A177" s="115"/>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A177" s="119"/>
       <c r="B177" s="16">
         <v>40</v>
       </c>
@@ -6153,8 +6154,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A178" s="119">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A178" s="120">
         <v>0</v>
       </c>
       <c r="B178" s="31">
@@ -6170,8 +6171,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A179" s="120"/>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A179" s="121"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
       <c r="D179" s="16">
@@ -6179,12 +6180,12 @@
       </c>
       <c r="E179" s="14"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A183" s="22"/>
       <c r="B183" s="23" t="s">
         <v>53</v>
@@ -6202,8 +6203,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A184" s="114" t="s">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A184" s="118" t="s">
         <v>23</v>
       </c>
       <c r="B184" s="13">
@@ -6222,8 +6223,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A185" s="115"/>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A185" s="119"/>
       <c r="B185" s="14"/>
       <c r="C185" s="16">
         <v>0</v>
@@ -6236,8 +6237,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A186" s="114" t="s">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A186" s="118" t="s">
         <v>79</v>
       </c>
       <c r="B186" s="13">
@@ -6256,8 +6257,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A187" s="115"/>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A187" s="119"/>
       <c r="B187" s="14"/>
       <c r="C187" s="16">
         <v>10</v>
@@ -6270,8 +6271,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A188" s="114" t="s">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A188" s="118" t="s">
         <v>80</v>
       </c>
       <c r="B188" s="18">
@@ -6290,8 +6291,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A189" s="115"/>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A189" s="119"/>
       <c r="B189" s="39"/>
       <c r="C189" s="40">
         <v>50</v>
@@ -6304,8 +6305,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A190" s="114" t="s">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A190" s="118" t="s">
         <v>58</v>
       </c>
       <c r="B190" s="15">
@@ -6324,8 +6325,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A191" s="115"/>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A191" s="119"/>
       <c r="B191" s="16">
         <v>40</v>
       </c>
@@ -6335,8 +6336,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A192" s="119" t="s">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A192" s="120" t="s">
         <v>81</v>
       </c>
       <c r="B192" s="31">
@@ -6352,8 +6353,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A193" s="120"/>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A193" s="121"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
       <c r="D193" s="16">
@@ -6361,12 +6362,12 @@
       </c>
       <c r="E193" s="14"/>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="42" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="22"/>
       <c r="B197" s="23" t="s">
         <v>53</v>
@@ -6381,8 +6382,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A198" s="114" t="s">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A198" s="118" t="s">
         <v>23</v>
       </c>
       <c r="B198" s="13">
@@ -6398,8 +6399,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A199" s="115"/>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A199" s="119"/>
       <c r="B199" s="14"/>
       <c r="C199" s="16" t="s">
         <v>37</v>
@@ -6409,8 +6410,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A200" s="114" t="s">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A200" s="118" t="s">
         <v>79</v>
       </c>
       <c r="B200" s="13">
@@ -6426,8 +6427,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A201" s="115"/>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A201" s="119"/>
       <c r="B201" s="14"/>
       <c r="C201" s="16">
         <v>10</v>
@@ -6437,8 +6438,8 @@
       </c>
       <c r="E201" s="14"/>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A202" s="114" t="s">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A202" s="118" t="s">
         <v>80</v>
       </c>
       <c r="B202" s="18">
@@ -6454,8 +6455,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A203" s="115"/>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A203" s="119"/>
       <c r="B203" s="39"/>
       <c r="C203" s="40" t="s">
         <v>40</v>
@@ -6465,8 +6466,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A204" s="114" t="s">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A204" s="118" t="s">
         <v>58</v>
       </c>
       <c r="B204" s="15">
@@ -6482,8 +6483,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A205" s="115"/>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A205" s="119"/>
       <c r="B205" s="16">
         <v>40</v>
       </c>
@@ -6493,8 +6494,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A206" s="119" t="s">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A206" s="120" t="s">
         <v>81</v>
       </c>
       <c r="B206" s="31">
@@ -6510,8 +6511,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A207" s="120"/>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A207" s="121"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
       <c r="D207" s="16">
@@ -6519,12 +6520,12 @@
       </c>
       <c r="E207" s="14"/>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A209" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A211" s="22" t="s">
         <v>5</v>
       </c>
@@ -6541,8 +6542,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A212" s="114">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A212" s="118">
         <v>0</v>
       </c>
       <c r="B212" s="13">
@@ -6558,8 +6559,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A213" s="115"/>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A213" s="119"/>
       <c r="B213" s="14"/>
       <c r="C213" s="16">
         <v>40</v>
@@ -6567,8 +6568,8 @@
       <c r="D213" s="14"/>
       <c r="E213" s="14"/>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A214" s="114">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A214" s="118">
         <v>0</v>
       </c>
       <c r="B214" s="13">
@@ -6584,8 +6585,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A215" s="115"/>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A215" s="119"/>
       <c r="B215" s="14"/>
       <c r="C215" s="16">
         <v>10</v>
@@ -6595,8 +6596,8 @@
       </c>
       <c r="E215" s="14"/>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A216" s="114">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A216" s="118">
         <v>0</v>
       </c>
       <c r="B216" s="18">
@@ -6612,8 +6613,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A217" s="115"/>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A217" s="119"/>
       <c r="B217" s="39"/>
       <c r="C217" s="40">
         <v>10</v>
@@ -6623,8 +6624,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A218" s="114">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A218" s="118">
         <v>0</v>
       </c>
       <c r="B218" s="15">
@@ -6640,8 +6641,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A219" s="115"/>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A219" s="119"/>
       <c r="B219" s="16">
         <v>40</v>
       </c>
@@ -6651,8 +6652,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A220" s="119">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A220" s="120">
         <v>0</v>
       </c>
       <c r="B220" s="31">
@@ -6668,8 +6669,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A221" s="120"/>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A221" s="121"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
       <c r="D221" s="16">
@@ -6677,12 +6678,12 @@
       </c>
       <c r="E221" s="14"/>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A223" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A225" s="22"/>
       <c r="B225" s="23" t="s">
         <v>86</v>
@@ -6700,8 +6701,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A226" s="114" t="s">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A226" s="118" t="s">
         <v>23</v>
       </c>
       <c r="B226" s="13">
@@ -6720,8 +6721,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A227" s="115"/>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A227" s="119"/>
       <c r="B227" s="14"/>
       <c r="C227" s="16">
         <v>40</v>
@@ -6732,8 +6733,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A228" s="114" t="s">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A228" s="118" t="s">
         <v>79</v>
       </c>
       <c r="B228" s="13">
@@ -6752,8 +6753,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A229" s="115"/>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A229" s="119"/>
       <c r="B229" s="14"/>
       <c r="C229" s="16">
         <v>10</v>
@@ -6766,8 +6767,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A230" s="114" t="s">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A230" s="118" t="s">
         <v>80</v>
       </c>
       <c r="B230" s="18">
@@ -6786,8 +6787,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A231" s="115"/>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A231" s="119"/>
       <c r="B231" s="39"/>
       <c r="C231" s="40">
         <v>10</v>
@@ -6800,8 +6801,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A232" s="114" t="s">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A232" s="118" t="s">
         <v>88</v>
       </c>
       <c r="B232" s="15">
@@ -6820,8 +6821,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A233" s="115"/>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A233" s="119"/>
       <c r="B233" s="16">
         <v>40</v>
       </c>
@@ -6831,8 +6832,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A234" s="119" t="s">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A234" s="120" t="s">
         <v>81</v>
       </c>
       <c r="B234" s="31">
@@ -6848,8 +6849,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A235" s="120"/>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A235" s="121"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
       <c r="D235" s="16">
@@ -6857,62 +6858,62 @@
       </c>
       <c r="E235" s="14"/>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A237" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A238" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A240" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A241" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A242" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A243" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A244" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A245" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A246" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A247" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A249" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A251" s="22" t="s">
         <v>5</v>
       </c>
@@ -6948,7 +6949,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A252" s="22">
         <v>40</v>
       </c>
@@ -6981,7 +6982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A253" s="22">
         <v>50</v>
       </c>
@@ -7014,7 +7015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A254" s="22">
         <v>50</v>
       </c>
@@ -7047,7 +7048,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A255" s="22">
         <v>40</v>
       </c>
@@ -7080,7 +7081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A256" s="44">
         <v>10</v>
       </c>
@@ -7113,7 +7114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.45">
       <c r="G258" s="46" t="s">
         <v>100</v>
       </c>
@@ -7122,12 +7123,12 @@
         <v>610</v>
       </c>
     </row>
-    <row r="260" spans="1:8" s="118" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A260" s="118" t="s">
+    <row r="260" spans="1:8" s="116" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A260" s="116" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A262" s="1" t="s">
         <v>102</v>
       </c>
@@ -7135,7 +7136,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A264" s="22" t="s">
         <v>5</v>
       </c>
@@ -7155,8 +7156,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A265" s="114">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A265" s="118">
         <v>20</v>
       </c>
       <c r="B265" s="8">
@@ -7175,16 +7176,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A266" s="115"/>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A266" s="119"/>
       <c r="B266" s="12"/>
       <c r="C266" s="12"/>
       <c r="D266" s="12"/>
       <c r="E266" s="12"/>
       <c r="F266" s="9"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A267" s="114">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A267" s="118">
         <v>50</v>
       </c>
       <c r="B267" s="8">
@@ -7203,16 +7204,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A268" s="115"/>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A268" s="119"/>
       <c r="B268" s="12"/>
       <c r="C268" s="12"/>
       <c r="D268" s="12"/>
       <c r="E268" s="50"/>
       <c r="F268" s="11"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A269" s="114">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A269" s="118">
         <v>50</v>
       </c>
       <c r="B269" s="10">
@@ -7231,16 +7232,16 @@
         <v>104</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A270" s="115"/>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A270" s="119"/>
       <c r="B270" s="38"/>
       <c r="C270" s="38"/>
       <c r="D270" s="38"/>
       <c r="E270" s="38"/>
       <c r="F270" s="11"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A271" s="114">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A271" s="118">
         <v>40</v>
       </c>
       <c r="B271" s="8">
@@ -7259,15 +7260,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A272" s="115"/>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A272" s="119"/>
       <c r="B272" s="12"/>
       <c r="C272" s="12"/>
       <c r="D272" s="12"/>
       <c r="E272" s="12"/>
       <c r="F272" s="11"/>
     </row>
-    <row r="273" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A273" s="53"/>
       <c r="B273" s="48"/>
       <c r="C273" s="48"/>
@@ -7275,7 +7276,7 @@
       <c r="E273" s="48"/>
       <c r="F273" s="48"/>
     </row>
-    <row r="274" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A274" s="22" t="s">
         <v>5</v>
       </c>
@@ -7421,8 +7422,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:55" x14ac:dyDescent="0.4">
-      <c r="A275" s="114">
+    <row r="275" spans="1:55" x14ac:dyDescent="0.45">
+      <c r="A275" s="118">
         <v>0</v>
       </c>
       <c r="B275" s="15">
@@ -7440,7 +7441,7 @@
       <c r="F275" s="30">
         <v>1</v>
       </c>
-      <c r="H275" s="114">
+      <c r="H275" s="118">
         <v>0</v>
       </c>
       <c r="I275" s="15">
@@ -7458,7 +7459,7 @@
       <c r="M275" s="30">
         <v>1</v>
       </c>
-      <c r="O275" s="114">
+      <c r="O275" s="118">
         <v>0</v>
       </c>
       <c r="P275" s="15">
@@ -7476,7 +7477,7 @@
       <c r="T275" s="30">
         <v>1</v>
       </c>
-      <c r="V275" s="114">
+      <c r="V275" s="118">
         <v>0</v>
       </c>
       <c r="W275" s="15">
@@ -7494,7 +7495,7 @@
       <c r="AA275" s="30">
         <v>1</v>
       </c>
-      <c r="AC275" s="114">
+      <c r="AC275" s="118">
         <v>0</v>
       </c>
       <c r="AD275" s="15">
@@ -7512,7 +7513,7 @@
       <c r="AH275" s="30">
         <v>1</v>
       </c>
-      <c r="AJ275" s="114">
+      <c r="AJ275" s="118">
         <v>0</v>
       </c>
       <c r="AK275" s="15">
@@ -7530,7 +7531,7 @@
       <c r="AO275" s="30">
         <v>1</v>
       </c>
-      <c r="AQ275" s="114">
+      <c r="AQ275" s="118">
         <v>0</v>
       </c>
       <c r="AR275" s="15">
@@ -7548,7 +7549,7 @@
       <c r="AV275" s="30">
         <v>1</v>
       </c>
-      <c r="AX275" s="114">
+      <c r="AX275" s="118">
         <v>0</v>
       </c>
       <c r="AY275" s="15">
@@ -7567,8 +7568,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:55" x14ac:dyDescent="0.4">
-      <c r="A276" s="115"/>
+    <row r="276" spans="1:55" x14ac:dyDescent="0.45">
+      <c r="A276" s="119"/>
       <c r="B276" s="16">
         <v>20</v>
       </c>
@@ -7576,7 +7577,7 @@
       <c r="D276" s="14"/>
       <c r="E276" s="14"/>
       <c r="F276" s="30"/>
-      <c r="H276" s="115"/>
+      <c r="H276" s="119"/>
       <c r="I276" s="16">
         <v>20</v>
       </c>
@@ -7584,7 +7585,7 @@
       <c r="K276" s="14"/>
       <c r="L276" s="14"/>
       <c r="M276" s="30"/>
-      <c r="O276" s="115"/>
+      <c r="O276" s="119"/>
       <c r="P276" s="16">
         <v>20</v>
       </c>
@@ -7592,7 +7593,7 @@
       <c r="R276" s="14"/>
       <c r="S276" s="14"/>
       <c r="T276" s="30"/>
-      <c r="V276" s="115"/>
+      <c r="V276" s="119"/>
       <c r="W276" s="16">
         <v>20</v>
       </c>
@@ -7600,7 +7601,7 @@
       <c r="Y276" s="14"/>
       <c r="Z276" s="14"/>
       <c r="AA276" s="30"/>
-      <c r="AC276" s="115"/>
+      <c r="AC276" s="119"/>
       <c r="AD276" s="16">
         <v>20</v>
       </c>
@@ -7608,7 +7609,7 @@
       <c r="AF276" s="14"/>
       <c r="AG276" s="14"/>
       <c r="AH276" s="30"/>
-      <c r="AJ276" s="115"/>
+      <c r="AJ276" s="119"/>
       <c r="AK276" s="16">
         <v>20</v>
       </c>
@@ -7616,7 +7617,7 @@
       <c r="AM276" s="14"/>
       <c r="AN276" s="14"/>
       <c r="AO276" s="30"/>
-      <c r="AQ276" s="115"/>
+      <c r="AQ276" s="119"/>
       <c r="AR276" s="16">
         <v>20</v>
       </c>
@@ -7624,7 +7625,7 @@
       <c r="AT276" s="14"/>
       <c r="AU276" s="14"/>
       <c r="AV276" s="30"/>
-      <c r="AX276" s="115"/>
+      <c r="AX276" s="119"/>
       <c r="AY276" s="16">
         <v>20</v>
       </c>
@@ -7633,8 +7634,8 @@
       <c r="BB276" s="14"/>
       <c r="BC276" s="30"/>
     </row>
-    <row r="277" spans="1:55" x14ac:dyDescent="0.4">
-      <c r="A277" s="114">
+    <row r="277" spans="1:55" x14ac:dyDescent="0.45">
+      <c r="A277" s="118">
         <v>50</v>
       </c>
       <c r="B277" s="8">
@@ -7652,7 +7653,7 @@
       <c r="F277" s="26">
         <v>9</v>
       </c>
-      <c r="H277" s="114">
+      <c r="H277" s="118">
         <v>10</v>
       </c>
       <c r="I277" s="8">
@@ -7670,7 +7671,7 @@
       <c r="M277" s="26">
         <v>9</v>
       </c>
-      <c r="O277" s="114">
+      <c r="O277" s="118">
         <v>0</v>
       </c>
       <c r="P277" s="13">
@@ -7688,7 +7689,7 @@
       <c r="T277" s="31">
         <v>9</v>
       </c>
-      <c r="V277" s="114">
+      <c r="V277" s="118">
         <v>0</v>
       </c>
       <c r="W277" s="13">
@@ -7706,7 +7707,7 @@
       <c r="AA277" s="31">
         <v>9</v>
       </c>
-      <c r="AC277" s="114">
+      <c r="AC277" s="118">
         <v>0</v>
       </c>
       <c r="AD277" s="13">
@@ -7724,7 +7725,7 @@
       <c r="AH277" s="31">
         <v>9</v>
       </c>
-      <c r="AJ277" s="114">
+      <c r="AJ277" s="118">
         <v>0</v>
       </c>
       <c r="AK277" s="13">
@@ -7742,7 +7743,7 @@
       <c r="AO277" s="31">
         <v>9</v>
       </c>
-      <c r="AQ277" s="114">
+      <c r="AQ277" s="118">
         <v>0</v>
       </c>
       <c r="AR277" s="13">
@@ -7760,7 +7761,7 @@
       <c r="AV277" s="31">
         <v>9</v>
       </c>
-      <c r="AX277" s="114">
+      <c r="AX277" s="118">
         <v>0</v>
       </c>
       <c r="AY277" s="13">
@@ -7779,14 +7780,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="278" spans="1:55" x14ac:dyDescent="0.4">
-      <c r="A278" s="115"/>
+    <row r="278" spans="1:55" x14ac:dyDescent="0.45">
+      <c r="A278" s="119"/>
       <c r="B278" s="12"/>
       <c r="C278" s="12"/>
       <c r="D278" s="12"/>
       <c r="E278" s="50"/>
       <c r="F278" s="11"/>
-      <c r="H278" s="115"/>
+      <c r="H278" s="119"/>
       <c r="I278" s="12"/>
       <c r="J278" s="16">
         <v>40</v>
@@ -7794,7 +7795,7 @@
       <c r="K278" s="12"/>
       <c r="L278" s="50"/>
       <c r="M278" s="11"/>
-      <c r="O278" s="115"/>
+      <c r="O278" s="119"/>
       <c r="P278" s="14"/>
       <c r="Q278" s="16">
         <v>40</v>
@@ -7804,7 +7805,7 @@
       </c>
       <c r="S278" s="55"/>
       <c r="T278" s="29"/>
-      <c r="V278" s="115"/>
+      <c r="V278" s="119"/>
       <c r="W278" s="14"/>
       <c r="X278" s="16">
         <v>40</v>
@@ -7814,7 +7815,7 @@
       </c>
       <c r="Z278" s="55"/>
       <c r="AA278" s="29"/>
-      <c r="AC278" s="115"/>
+      <c r="AC278" s="119"/>
       <c r="AD278" s="14"/>
       <c r="AE278" s="16">
         <v>40</v>
@@ -7824,7 +7825,7 @@
       </c>
       <c r="AG278" s="55"/>
       <c r="AH278" s="29"/>
-      <c r="AJ278" s="115"/>
+      <c r="AJ278" s="119"/>
       <c r="AK278" s="14"/>
       <c r="AL278" s="16">
         <v>40</v>
@@ -7834,7 +7835,7 @@
       </c>
       <c r="AN278" s="55"/>
       <c r="AO278" s="29"/>
-      <c r="AQ278" s="115"/>
+      <c r="AQ278" s="119"/>
       <c r="AR278" s="14"/>
       <c r="AS278" s="16">
         <v>40</v>
@@ -7844,7 +7845,7 @@
       </c>
       <c r="AU278" s="55"/>
       <c r="AV278" s="29"/>
-      <c r="AX278" s="115"/>
+      <c r="AX278" s="119"/>
       <c r="AY278" s="14"/>
       <c r="AZ278" s="16">
         <v>40</v>
@@ -7855,8 +7856,8 @@
       <c r="BB278" s="55"/>
       <c r="BC278" s="29"/>
     </row>
-    <row r="279" spans="1:55" x14ac:dyDescent="0.4">
-      <c r="A279" s="114">
+    <row r="279" spans="1:55" x14ac:dyDescent="0.45">
+      <c r="A279" s="118">
         <v>50</v>
       </c>
       <c r="B279" s="10">
@@ -7874,7 +7875,7 @@
       <c r="F279" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="H279" s="114">
+      <c r="H279" s="118">
         <v>50</v>
       </c>
       <c r="I279" s="10">
@@ -7892,7 +7893,7 @@
       <c r="M279" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="O279" s="114">
+      <c r="O279" s="118">
         <v>50</v>
       </c>
       <c r="P279" s="10">
@@ -7910,7 +7911,7 @@
       <c r="T279" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="V279" s="114">
+      <c r="V279" s="118">
         <v>50</v>
       </c>
       <c r="W279" s="18">
@@ -7928,7 +7929,7 @@
       <c r="AA279" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="AC279" s="114">
+      <c r="AC279" s="118">
         <v>30</v>
       </c>
       <c r="AD279" s="18">
@@ -7946,7 +7947,7 @@
       <c r="AH279" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="AJ279" s="114">
+      <c r="AJ279" s="118">
         <v>30</v>
       </c>
       <c r="AK279" s="18">
@@ -7964,7 +7965,7 @@
       <c r="AO279" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="AQ279" s="114">
+      <c r="AQ279" s="118">
         <v>0</v>
       </c>
       <c r="AR279" s="18">
@@ -7982,7 +7983,7 @@
       <c r="AV279" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="AX279" s="114">
+      <c r="AX279" s="118">
         <v>0</v>
       </c>
       <c r="AY279" s="18">
@@ -8001,32 +8002,32 @@
         <v>104</v>
       </c>
     </row>
-    <row r="280" spans="1:55" x14ac:dyDescent="0.4">
-      <c r="A280" s="115"/>
+    <row r="280" spans="1:55" x14ac:dyDescent="0.45">
+      <c r="A280" s="119"/>
       <c r="B280" s="38"/>
       <c r="C280" s="38"/>
       <c r="D280" s="38"/>
       <c r="E280" s="38"/>
       <c r="F280" s="11"/>
-      <c r="H280" s="115"/>
+      <c r="H280" s="119"/>
       <c r="I280" s="38"/>
       <c r="J280" s="39"/>
       <c r="K280" s="38"/>
       <c r="L280" s="38"/>
       <c r="M280" s="11"/>
-      <c r="O280" s="115"/>
+      <c r="O280" s="119"/>
       <c r="P280" s="38"/>
       <c r="Q280" s="39"/>
       <c r="R280" s="58"/>
       <c r="S280" s="38"/>
       <c r="T280" s="11"/>
-      <c r="V280" s="115"/>
+      <c r="V280" s="119"/>
       <c r="W280" s="39"/>
       <c r="X280" s="39"/>
       <c r="Y280" s="58"/>
       <c r="Z280" s="38"/>
       <c r="AA280" s="11"/>
-      <c r="AC280" s="115"/>
+      <c r="AC280" s="119"/>
       <c r="AD280" s="39"/>
       <c r="AE280" s="39"/>
       <c r="AF280" s="58"/>
@@ -8034,7 +8035,7 @@
         <v>20</v>
       </c>
       <c r="AH280" s="11"/>
-      <c r="AJ280" s="115"/>
+      <c r="AJ280" s="119"/>
       <c r="AK280" s="39"/>
       <c r="AL280" s="39"/>
       <c r="AM280" s="58"/>
@@ -8042,7 +8043,7 @@
         <v>20</v>
       </c>
       <c r="AO280" s="29"/>
-      <c r="AQ280" s="115"/>
+      <c r="AQ280" s="119"/>
       <c r="AR280" s="39"/>
       <c r="AS280" s="39"/>
       <c r="AT280" s="40">
@@ -8052,7 +8053,7 @@
         <v>20</v>
       </c>
       <c r="AV280" s="29"/>
-      <c r="AX280" s="115"/>
+      <c r="AX280" s="119"/>
       <c r="AY280" s="39"/>
       <c r="AZ280" s="39"/>
       <c r="BA280" s="40">
@@ -8063,8 +8064,8 @@
       </c>
       <c r="BC280" s="29"/>
     </row>
-    <row r="281" spans="1:55" x14ac:dyDescent="0.4">
-      <c r="A281" s="114">
+    <row r="281" spans="1:55" x14ac:dyDescent="0.45">
+      <c r="A281" s="118">
         <v>40</v>
       </c>
       <c r="B281" s="8">
@@ -8082,7 +8083,7 @@
       <c r="F281" s="9">
         <v>6</v>
       </c>
-      <c r="H281" s="114">
+      <c r="H281" s="118">
         <v>40</v>
       </c>
       <c r="I281" s="8">
@@ -8100,7 +8101,7 @@
       <c r="M281" s="9">
         <v>6</v>
       </c>
-      <c r="O281" s="114">
+      <c r="O281" s="118">
         <v>40</v>
       </c>
       <c r="P281" s="8">
@@ -8118,7 +8119,7 @@
       <c r="T281" s="9">
         <v>6</v>
       </c>
-      <c r="V281" s="114">
+      <c r="V281" s="118">
         <v>20</v>
       </c>
       <c r="W281" s="15">
@@ -8136,7 +8137,7 @@
       <c r="AA281" s="9">
         <v>6</v>
       </c>
-      <c r="AC281" s="114">
+      <c r="AC281" s="118">
         <v>20</v>
       </c>
       <c r="AD281" s="15">
@@ -8154,7 +8155,7 @@
       <c r="AH281" s="9">
         <v>6</v>
       </c>
-      <c r="AJ281" s="114">
+      <c r="AJ281" s="118">
         <v>0</v>
       </c>
       <c r="AK281" s="15">
@@ -8172,7 +8173,7 @@
       <c r="AO281" s="32">
         <v>6</v>
       </c>
-      <c r="AQ281" s="114">
+      <c r="AQ281" s="118">
         <v>0</v>
       </c>
       <c r="AR281" s="15">
@@ -8190,7 +8191,7 @@
       <c r="AV281" s="32">
         <v>6</v>
       </c>
-      <c r="AX281" s="114">
+      <c r="AX281" s="118">
         <v>0</v>
       </c>
       <c r="AY281" s="15">
@@ -8209,26 +8210,26 @@
         <v>6</v>
       </c>
     </row>
-    <row r="282" spans="1:55" x14ac:dyDescent="0.4">
-      <c r="A282" s="115"/>
+    <row r="282" spans="1:55" x14ac:dyDescent="0.45">
+      <c r="A282" s="119"/>
       <c r="B282" s="12"/>
       <c r="C282" s="12"/>
       <c r="D282" s="12"/>
       <c r="E282" s="12"/>
       <c r="F282" s="11"/>
-      <c r="H282" s="115"/>
+      <c r="H282" s="119"/>
       <c r="I282" s="12"/>
       <c r="J282" s="14"/>
       <c r="K282" s="12"/>
       <c r="L282" s="12"/>
       <c r="M282" s="11"/>
-      <c r="O282" s="115"/>
+      <c r="O282" s="119"/>
       <c r="P282" s="12"/>
       <c r="Q282" s="14"/>
       <c r="R282" s="20"/>
       <c r="S282" s="12"/>
       <c r="T282" s="11"/>
-      <c r="V282" s="115"/>
+      <c r="V282" s="119"/>
       <c r="W282" s="16">
         <v>20</v>
       </c>
@@ -8236,7 +8237,7 @@
       <c r="Y282" s="20"/>
       <c r="Z282" s="12"/>
       <c r="AA282" s="11"/>
-      <c r="AC282" s="115"/>
+      <c r="AC282" s="119"/>
       <c r="AD282" s="16">
         <v>20</v>
       </c>
@@ -8244,7 +8245,7 @@
       <c r="AF282" s="20"/>
       <c r="AG282" s="14"/>
       <c r="AH282" s="12"/>
-      <c r="AJ282" s="115"/>
+      <c r="AJ282" s="119"/>
       <c r="AK282" s="16">
         <v>20</v>
       </c>
@@ -8254,7 +8255,7 @@
       <c r="AO282" s="16">
         <v>20</v>
       </c>
-      <c r="AQ282" s="115"/>
+      <c r="AQ282" s="119"/>
       <c r="AR282" s="16">
         <v>20</v>
       </c>
@@ -8264,7 +8265,7 @@
       <c r="AV282" s="16">
         <v>20</v>
       </c>
-      <c r="AX282" s="115"/>
+      <c r="AX282" s="119"/>
       <c r="AY282" s="16">
         <v>20</v>
       </c>
@@ -8275,8 +8276,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="283" spans="1:55" x14ac:dyDescent="0.4">
-      <c r="A283" s="116">
+    <row r="283" spans="1:55" x14ac:dyDescent="0.45">
+      <c r="A283" s="122">
         <v>10</v>
       </c>
       <c r="B283" s="24">
@@ -8294,7 +8295,7 @@
       <c r="F283" s="25">
         <v>0</v>
       </c>
-      <c r="H283" s="116">
+      <c r="H283" s="122">
         <v>10</v>
       </c>
       <c r="I283" s="24">
@@ -8312,7 +8313,7 @@
       <c r="M283" s="25">
         <v>0</v>
       </c>
-      <c r="O283" s="116">
+      <c r="O283" s="122">
         <v>10</v>
       </c>
       <c r="P283" s="24">
@@ -8330,7 +8331,7 @@
       <c r="T283" s="25">
         <v>0</v>
       </c>
-      <c r="V283" s="116">
+      <c r="V283" s="122">
         <v>10</v>
       </c>
       <c r="W283" s="56">
@@ -8348,7 +8349,7 @@
       <c r="AA283" s="25">
         <v>0</v>
       </c>
-      <c r="AC283" s="116">
+      <c r="AC283" s="122">
         <v>10</v>
       </c>
       <c r="AD283" s="56">
@@ -8366,7 +8367,7 @@
       <c r="AH283" s="25">
         <v>0</v>
       </c>
-      <c r="AJ283" s="116">
+      <c r="AJ283" s="122">
         <v>10</v>
       </c>
       <c r="AK283" s="56">
@@ -8384,7 +8385,7 @@
       <c r="AO283" s="61">
         <v>0</v>
       </c>
-      <c r="AQ283" s="116">
+      <c r="AQ283" s="122">
         <v>10</v>
       </c>
       <c r="AR283" s="56">
@@ -8402,7 +8403,7 @@
       <c r="AV283" s="61">
         <v>0</v>
       </c>
-      <c r="AX283" s="116">
+      <c r="AX283" s="122">
         <v>0</v>
       </c>
       <c r="AY283" s="56">
@@ -8421,50 +8422,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:55" x14ac:dyDescent="0.4">
-      <c r="A284" s="117"/>
+    <row r="284" spans="1:55" x14ac:dyDescent="0.45">
+      <c r="A284" s="123"/>
       <c r="B284" s="6"/>
       <c r="C284" s="11"/>
       <c r="D284" s="6"/>
       <c r="E284" s="11"/>
       <c r="F284" s="7"/>
-      <c r="H284" s="117"/>
+      <c r="H284" s="123"/>
       <c r="I284" s="6"/>
       <c r="J284" s="29"/>
       <c r="K284" s="6"/>
       <c r="L284" s="11"/>
       <c r="M284" s="7"/>
-      <c r="O284" s="117"/>
+      <c r="O284" s="123"/>
       <c r="P284" s="6"/>
       <c r="Q284" s="29"/>
       <c r="R284" s="60"/>
       <c r="S284" s="11"/>
       <c r="T284" s="7"/>
-      <c r="V284" s="117"/>
+      <c r="V284" s="123"/>
       <c r="W284" s="57"/>
       <c r="X284" s="29"/>
       <c r="Y284" s="60"/>
       <c r="Z284" s="11"/>
       <c r="AA284" s="7"/>
-      <c r="AC284" s="117"/>
+      <c r="AC284" s="123"/>
       <c r="AD284" s="57"/>
       <c r="AE284" s="29"/>
       <c r="AF284" s="60"/>
       <c r="AG284" s="29"/>
       <c r="AH284" s="7"/>
-      <c r="AJ284" s="117"/>
+      <c r="AJ284" s="123"/>
       <c r="AK284" s="57"/>
       <c r="AL284" s="29"/>
       <c r="AM284" s="60"/>
       <c r="AN284" s="29"/>
       <c r="AO284" s="62"/>
-      <c r="AQ284" s="117"/>
+      <c r="AQ284" s="123"/>
       <c r="AR284" s="57"/>
       <c r="AS284" s="29"/>
       <c r="AT284" s="60"/>
       <c r="AU284" s="29"/>
       <c r="AV284" s="62"/>
-      <c r="AX284" s="117"/>
+      <c r="AX284" s="123"/>
       <c r="AY284" s="57"/>
       <c r="AZ284" s="29"/>
       <c r="BA284" s="66">
@@ -8473,12 +8474,12 @@
       <c r="BB284" s="29"/>
       <c r="BC284" s="62"/>
     </row>
-    <row r="286" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A286" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="288" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:55" x14ac:dyDescent="0.45">
       <c r="A288" s="22" t="s">
         <v>5</v>
       </c>
@@ -8498,8 +8499,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A289" s="114">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A289" s="118">
         <v>0</v>
       </c>
       <c r="B289" s="15">
@@ -8518,8 +8519,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A290" s="115"/>
+    <row r="290" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A290" s="119"/>
       <c r="B290" s="16">
         <v>20</v>
       </c>
@@ -8530,8 +8531,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A291" s="114">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A291" s="118">
         <v>0</v>
       </c>
       <c r="B291" s="13">
@@ -8550,8 +8551,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A292" s="115"/>
+    <row r="292" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A292" s="119"/>
       <c r="B292" s="14"/>
       <c r="C292" s="16">
         <v>40</v>
@@ -8562,8 +8563,8 @@
       <c r="E292" s="55"/>
       <c r="F292" s="29"/>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A293" s="114">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A293" s="118">
         <v>0</v>
       </c>
       <c r="B293" s="18">
@@ -8582,8 +8583,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A294" s="115"/>
+    <row r="294" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A294" s="119"/>
       <c r="B294" s="39"/>
       <c r="C294" s="39"/>
       <c r="D294" s="40">
@@ -8594,8 +8595,8 @@
       </c>
       <c r="F294" s="29"/>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A295" s="114">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A295" s="118">
         <v>0</v>
       </c>
       <c r="B295" s="15">
@@ -8614,8 +8615,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A296" s="115"/>
+    <row r="296" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A296" s="119"/>
       <c r="B296" s="16">
         <v>20</v>
       </c>
@@ -8626,8 +8627,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A297" s="116">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A297" s="122">
         <v>0</v>
       </c>
       <c r="B297" s="56">
@@ -8646,8 +8647,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A298" s="117"/>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A298" s="123"/>
       <c r="B298" s="57"/>
       <c r="C298" s="29"/>
       <c r="D298" s="66">
@@ -8658,7 +8659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A300" s="53" t="s">
         <v>117</v>
       </c>
@@ -8677,7 +8678,7 @@
       <c r="N300" s="53"/>
       <c r="O300" s="53"/>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A301" s="53" t="s">
         <v>118</v>
       </c>
@@ -8696,7 +8697,7 @@
       <c r="N301" s="53"/>
       <c r="O301" s="53"/>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A302" s="53"/>
       <c r="B302" s="53"/>
       <c r="C302" s="53"/>
@@ -8713,7 +8714,7 @@
       <c r="N302" s="53"/>
       <c r="O302" s="53"/>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A303" s="53" t="s">
         <v>10</v>
       </c>
@@ -8732,7 +8733,7 @@
       <c r="N303" s="53"/>
       <c r="O303" s="53"/>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.45">
       <c r="G304" s="53"/>
       <c r="H304" s="53"/>
       <c r="I304" s="53"/>
@@ -8743,7 +8744,7 @@
       <c r="N304" s="53"/>
       <c r="O304" s="53"/>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A305" s="22" t="s">
         <v>5</v>
       </c>
@@ -8772,7 +8773,7 @@
       <c r="N305" s="53"/>
       <c r="O305" s="53"/>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A306" s="34" t="s">
         <v>23</v>
       </c>
@@ -8801,7 +8802,7 @@
       <c r="N306" s="53"/>
       <c r="O306" s="53"/>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A307" s="35"/>
       <c r="B307" s="16">
         <v>20</v>
@@ -8824,7 +8825,7 @@
       <c r="N307" s="53"/>
       <c r="O307" s="53"/>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A308" s="34" t="s">
         <v>24</v>
       </c>
@@ -8853,7 +8854,7 @@
       <c r="N308" s="53"/>
       <c r="O308" s="53"/>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A309" s="35"/>
       <c r="B309" s="14"/>
       <c r="C309" s="16">
@@ -8874,7 +8875,7 @@
       <c r="N309" s="53"/>
       <c r="O309" s="53"/>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A310" s="34" t="s">
         <v>107</v>
       </c>
@@ -8903,7 +8904,7 @@
       <c r="N310" s="53"/>
       <c r="O310" s="53"/>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A311" s="35"/>
       <c r="B311" s="39" t="s">
         <v>119</v>
@@ -8928,7 +8929,7 @@
       <c r="N311" s="53"/>
       <c r="O311" s="53"/>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A312" s="34" t="s">
         <v>108</v>
       </c>
@@ -8957,7 +8958,7 @@
       <c r="N312" s="53"/>
       <c r="O312" s="53"/>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A313" s="35"/>
       <c r="B313" s="16" t="s">
         <v>114</v>
@@ -8978,7 +8979,7 @@
       <c r="N313" s="53"/>
       <c r="O313" s="53"/>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A314" s="63" t="s">
         <v>27</v>
       </c>
@@ -9007,7 +9008,7 @@
       <c r="N314" s="53"/>
       <c r="O314" s="53"/>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A315" s="64"/>
       <c r="B315" s="57"/>
       <c r="C315" s="29"/>
@@ -9030,7 +9031,7 @@
       <c r="N315" s="53"/>
       <c r="O315" s="53"/>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A316" s="53"/>
       <c r="B316" s="53"/>
       <c r="C316" s="53"/>
@@ -9047,7 +9048,7 @@
       <c r="N316" s="53"/>
       <c r="O316" s="53"/>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A317" s="53" t="s">
         <v>42</v>
       </c>
@@ -9066,7 +9067,7 @@
       <c r="N317" s="53"/>
       <c r="O317" s="53"/>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A318" s="53"/>
       <c r="B318" s="53"/>
       <c r="C318" s="53"/>
@@ -9083,7 +9084,7 @@
       <c r="N318" s="53"/>
       <c r="O318" s="53"/>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A319" s="22" t="s">
         <v>5</v>
       </c>
@@ -9112,7 +9113,7 @@
       <c r="N319" s="53"/>
       <c r="O319" s="53"/>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A320" s="34">
         <v>0</v>
       </c>
@@ -9141,7 +9142,7 @@
       <c r="N320" s="53"/>
       <c r="O320" s="53"/>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A321" s="35"/>
       <c r="B321" s="16">
         <v>20</v>
@@ -9162,7 +9163,7 @@
       <c r="N321" s="53"/>
       <c r="O321" s="53"/>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A322" s="34">
         <v>0</v>
       </c>
@@ -9191,7 +9192,7 @@
       <c r="N322" s="53"/>
       <c r="O322" s="53"/>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A323" s="35"/>
       <c r="B323" s="14"/>
       <c r="C323" s="16">
@@ -9212,7 +9213,7 @@
       <c r="N323" s="53"/>
       <c r="O323" s="53"/>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A324" s="34">
         <v>0</v>
       </c>
@@ -9241,7 +9242,7 @@
       <c r="N324" s="53"/>
       <c r="O324" s="53"/>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A325" s="35"/>
       <c r="B325" s="40">
         <v>0</v>
@@ -9264,7 +9265,7 @@
       <c r="N325" s="53"/>
       <c r="O325" s="53"/>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A326" s="34">
         <v>0</v>
       </c>
@@ -9293,7 +9294,7 @@
       <c r="N326" s="53"/>
       <c r="O326" s="53"/>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A327" s="35"/>
       <c r="B327" s="16">
         <v>20</v>
@@ -9314,7 +9315,7 @@
       <c r="N327" s="53"/>
       <c r="O327" s="53"/>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A328" s="63">
         <v>0</v>
       </c>
@@ -9343,7 +9344,7 @@
       <c r="N328" s="53"/>
       <c r="O328" s="53"/>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A329" s="64"/>
       <c r="B329" s="57"/>
       <c r="C329" s="29"/>
@@ -9364,7 +9365,7 @@
       <c r="N329" s="53"/>
       <c r="O329" s="53"/>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A330" s="53"/>
       <c r="B330" s="53"/>
       <c r="C330" s="53"/>
@@ -9381,7 +9382,7 @@
       <c r="N330" s="53"/>
       <c r="O330" s="53"/>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A331" s="53" t="s">
         <v>10</v>
       </c>
@@ -9400,7 +9401,7 @@
       <c r="N331" s="53"/>
       <c r="O331" s="53"/>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A332" s="53"/>
       <c r="B332" s="53"/>
       <c r="C332" s="53"/>
@@ -9417,7 +9418,7 @@
       <c r="N332" s="53"/>
       <c r="O332" s="53"/>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A333" s="22"/>
       <c r="B333" s="23" t="s">
         <v>19</v>
@@ -9446,7 +9447,7 @@
       <c r="N333" s="53"/>
       <c r="O333" s="53"/>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A334" s="34" t="s">
         <v>23</v>
       </c>
@@ -9477,7 +9478,7 @@
       <c r="N334" s="53"/>
       <c r="O334" s="53"/>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A335" s="35"/>
       <c r="B335" s="16">
         <v>20</v>
@@ -9504,7 +9505,7 @@
       <c r="N335" s="53"/>
       <c r="O335" s="53"/>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A336" s="34" t="s">
         <v>130</v>
       </c>
@@ -9535,7 +9536,7 @@
       <c r="N336" s="53"/>
       <c r="O336" s="53"/>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A337" s="35"/>
       <c r="B337" s="14"/>
       <c r="C337" s="16">
@@ -9558,7 +9559,7 @@
       <c r="N337" s="53"/>
       <c r="O337" s="53"/>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A338" s="34" t="s">
         <v>25</v>
       </c>
@@ -9589,7 +9590,7 @@
       <c r="N338" s="53"/>
       <c r="O338" s="53"/>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A339" s="35"/>
       <c r="B339" s="40">
         <v>0</v>
@@ -9616,7 +9617,7 @@
       <c r="N339" s="53"/>
       <c r="O339" s="53"/>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A340" s="34" t="s">
         <v>108</v>
       </c>
@@ -9647,7 +9648,7 @@
       <c r="N340" s="53"/>
       <c r="O340" s="53"/>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A341" s="35"/>
       <c r="B341" s="16">
         <v>20</v>
@@ -9670,7 +9671,7 @@
       <c r="N341" s="53"/>
       <c r="O341" s="53"/>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A342" s="63" t="s">
         <v>131</v>
       </c>
@@ -9699,7 +9700,7 @@
       <c r="N342" s="53"/>
       <c r="O342" s="53"/>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A343" s="64"/>
       <c r="B343" s="57"/>
       <c r="C343" s="29"/>
@@ -9720,7 +9721,7 @@
       <c r="N343" s="53"/>
       <c r="O343" s="53"/>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A344" s="53"/>
       <c r="B344" s="53"/>
       <c r="C344" s="53"/>
@@ -9737,7 +9738,7 @@
       <c r="N344" s="53"/>
       <c r="O344" s="53"/>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A345" s="53" t="s">
         <v>132</v>
       </c>
@@ -9756,7 +9757,7 @@
       <c r="N345" s="53"/>
       <c r="O345" s="53"/>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A346" s="53"/>
       <c r="B346" s="53"/>
       <c r="C346" s="53"/>
@@ -9773,7 +9774,7 @@
       <c r="N346" s="53"/>
       <c r="O346" s="53"/>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A347" s="22"/>
       <c r="B347" s="23" t="s">
         <v>19</v>
@@ -9800,7 +9801,7 @@
       <c r="N347" s="53"/>
       <c r="O347" s="53"/>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A348" s="34" t="s">
         <v>23</v>
       </c>
@@ -9829,7 +9830,7 @@
       <c r="N348" s="53"/>
       <c r="O348" s="53"/>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A349" s="35"/>
       <c r="B349" s="16" t="s">
         <v>114</v>
@@ -9854,7 +9855,7 @@
       <c r="N349" s="53"/>
       <c r="O349" s="53"/>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A350" s="34" t="s">
         <v>130</v>
       </c>
@@ -9883,7 +9884,7 @@
       <c r="N350" s="53"/>
       <c r="O350" s="53"/>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A351" s="35"/>
       <c r="B351" s="14"/>
       <c r="C351" s="16" t="s">
@@ -9904,7 +9905,7 @@
       <c r="N351" s="53"/>
       <c r="O351" s="53"/>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A352" s="34" t="s">
         <v>25</v>
       </c>
@@ -9933,7 +9934,7 @@
       <c r="N352" s="53"/>
       <c r="O352" s="53"/>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A353" s="35"/>
       <c r="B353" s="40" t="s">
         <v>37</v>
@@ -9949,7 +9950,7 @@
       </c>
       <c r="F353" s="29"/>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A354" s="34" t="s">
         <v>108</v>
       </c>
@@ -9969,7 +9970,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A355" s="35"/>
       <c r="B355" s="16">
         <v>20</v>
@@ -9981,7 +9982,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A356" s="63" t="s">
         <v>131</v>
       </c>
@@ -10001,7 +10002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A357" s="64"/>
       <c r="B357" s="57"/>
       <c r="C357" s="29"/>
@@ -10016,12 +10017,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A359" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A361" s="22" t="s">
         <v>5</v>
       </c>
@@ -10042,7 +10043,7 @@
       </c>
       <c r="H361" s="41"/>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A362" s="34">
         <v>0</v>
       </c>
@@ -10063,7 +10064,7 @@
       </c>
       <c r="H362" s="41"/>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A363" s="35"/>
       <c r="B363" s="14"/>
       <c r="C363" s="16">
@@ -10074,7 +10075,7 @@
       <c r="F363" s="14"/>
       <c r="H363" s="41"/>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A364" s="34">
         <v>0</v>
       </c>
@@ -10095,7 +10096,7 @@
       </c>
       <c r="H364" s="41"/>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A365" s="35"/>
       <c r="B365" s="14"/>
       <c r="C365" s="16">
@@ -10108,7 +10109,7 @@
       <c r="F365" s="29"/>
       <c r="H365" s="41"/>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A366" s="34">
         <v>0</v>
       </c>
@@ -10129,7 +10130,7 @@
       </c>
       <c r="H366" s="41"/>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A367" s="35"/>
       <c r="B367" s="40">
         <v>20</v>
@@ -10144,7 +10145,7 @@
       <c r="F367" s="29"/>
       <c r="H367" s="41"/>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A368" s="34">
         <v>0</v>
       </c>
@@ -10165,7 +10166,7 @@
       </c>
       <c r="H368" s="41"/>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A369" s="35"/>
       <c r="B369" s="16">
         <v>20</v>
@@ -10178,7 +10179,7 @@
       </c>
       <c r="H369" s="41"/>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A370" s="63">
         <v>0</v>
       </c>
@@ -10198,7 +10199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A371" s="64"/>
       <c r="B371" s="57"/>
       <c r="C371" s="29"/>
@@ -10210,12 +10211,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A373" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A375" s="22" t="s">
         <v>5</v>
       </c>
@@ -10238,7 +10239,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A376" s="34" t="s">
         <v>23</v>
       </c>
@@ -10261,7 +10262,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A377" s="35"/>
       <c r="B377" s="14"/>
       <c r="C377" s="16">
@@ -10274,7 +10275,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A378" s="34" t="s">
         <v>79</v>
       </c>
@@ -10297,7 +10298,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A379" s="35"/>
       <c r="B379" s="14"/>
       <c r="C379" s="16">
@@ -10312,7 +10313,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A380" s="34" t="s">
         <v>143</v>
       </c>
@@ -10335,7 +10336,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A381" s="35"/>
       <c r="B381" s="40">
         <v>20</v>
@@ -10354,7 +10355,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A382" s="34" t="s">
         <v>144</v>
       </c>
@@ -10377,7 +10378,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A383" s="35"/>
       <c r="B383" s="16">
         <v>20</v>
@@ -10392,7 +10393,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A384" s="63" t="s">
         <v>81</v>
       </c>
@@ -10412,7 +10413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A385" s="64"/>
       <c r="B385" s="57"/>
       <c r="C385" s="29"/>
@@ -10424,12 +10425,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A387" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A389" s="22"/>
       <c r="B389" s="23" t="s">
         <v>140</v>
@@ -10447,7 +10448,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A390" s="34" t="s">
         <v>23</v>
       </c>
@@ -10467,7 +10468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A391" s="35"/>
       <c r="B391" s="14"/>
       <c r="C391" s="16">
@@ -10477,7 +10478,7 @@
       <c r="E391" s="14"/>
       <c r="F391" s="14"/>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A392" s="34" t="s">
         <v>79</v>
       </c>
@@ -10497,7 +10498,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A393" s="35"/>
       <c r="B393" s="14"/>
       <c r="C393" s="16" t="s">
@@ -10509,7 +10510,7 @@
       <c r="E393" s="55"/>
       <c r="F393" s="29"/>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A394" s="34" t="s">
         <v>143</v>
       </c>
@@ -10529,7 +10530,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A395" s="35"/>
       <c r="B395" s="40">
         <v>20</v>
@@ -10545,7 +10546,7 @@
       </c>
       <c r="F395" s="29"/>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A396" s="34" t="s">
         <v>144</v>
       </c>
@@ -10565,7 +10566,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A397" s="35"/>
       <c r="B397" s="16">
         <v>20</v>
@@ -10577,7 +10578,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A398" s="63" t="s">
         <v>81</v>
       </c>
@@ -10597,7 +10598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A399" s="64"/>
       <c r="B399" s="57"/>
       <c r="C399" s="29"/>
@@ -10612,12 +10613,12 @@
         <v>146</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A401" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A403" s="22" t="s">
         <v>5</v>
       </c>
@@ -10637,7 +10638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A404" s="34">
         <v>0</v>
       </c>
@@ -10657,7 +10658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A405" s="35"/>
       <c r="B405" s="14"/>
       <c r="C405" s="16">
@@ -10667,7 +10668,7 @@
       <c r="E405" s="14"/>
       <c r="F405" s="14"/>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A406" s="34">
         <v>0</v>
       </c>
@@ -10687,7 +10688,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A407" s="35"/>
       <c r="B407" s="14"/>
       <c r="C407" s="16">
@@ -10699,7 +10700,7 @@
       <c r="E407" s="55"/>
       <c r="F407" s="29"/>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A408" s="34">
         <v>0</v>
       </c>
@@ -10719,7 +10720,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A409" s="35"/>
       <c r="B409" s="40">
         <v>20</v>
@@ -10733,7 +10734,7 @@
       </c>
       <c r="F409" s="29"/>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A410" s="34">
         <v>0</v>
       </c>
@@ -10753,7 +10754,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A411" s="35"/>
       <c r="B411" s="16">
         <v>20</v>
@@ -10765,7 +10766,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A412" s="63">
         <v>0</v>
       </c>
@@ -10785,7 +10786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A413" s="64"/>
       <c r="B413" s="57"/>
       <c r="C413" s="29"/>
@@ -10797,12 +10798,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A415" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A417" s="22"/>
       <c r="B417" s="23" t="s">
         <v>147</v>
@@ -10823,7 +10824,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A418" s="34" t="s">
         <v>23</v>
       </c>
@@ -10846,7 +10847,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A419" s="35"/>
       <c r="B419" s="14"/>
       <c r="C419" s="16">
@@ -10859,7 +10860,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A420" s="34" t="s">
         <v>79</v>
       </c>
@@ -10882,7 +10883,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A421" s="35"/>
       <c r="B421" s="14"/>
       <c r="C421" s="16">
@@ -10897,7 +10898,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A422" s="34" t="s">
         <v>80</v>
       </c>
@@ -10920,7 +10921,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A423" s="35"/>
       <c r="B423" s="40">
         <v>20</v>
@@ -10937,7 +10938,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A424" s="34" t="s">
         <v>149</v>
       </c>
@@ -10960,7 +10961,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A425" s="35"/>
       <c r="B425" s="16">
         <v>20</v>
@@ -10975,7 +10976,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A426" s="63" t="s">
         <v>81</v>
       </c>
@@ -10995,7 +10996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A427" s="64"/>
       <c r="B427" s="57"/>
       <c r="C427" s="29"/>
@@ -11007,12 +11008,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A429" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A431" s="22"/>
       <c r="B431" s="23" t="s">
         <v>147</v>
@@ -11030,7 +11031,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A432" s="34" t="s">
         <v>23</v>
       </c>
@@ -11050,7 +11051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A433" s="35"/>
       <c r="B433" s="14"/>
       <c r="C433" s="16" t="s">
@@ -11062,7 +11063,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A434" s="34" t="s">
         <v>79</v>
       </c>
@@ -11082,7 +11083,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A435" s="35"/>
       <c r="B435" s="14"/>
       <c r="C435" s="16">
@@ -11094,7 +11095,7 @@
       <c r="E435" s="55"/>
       <c r="F435" s="29"/>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A436" s="34" t="s">
         <v>80</v>
       </c>
@@ -11114,7 +11115,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A437" s="35"/>
       <c r="B437" s="40" t="s">
         <v>114</v>
@@ -11128,7 +11129,7 @@
       </c>
       <c r="F437" s="29"/>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A438" s="34" t="s">
         <v>149</v>
       </c>
@@ -11148,7 +11149,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A439" s="35"/>
       <c r="B439" s="16" t="s">
         <v>116</v>
@@ -11160,7 +11161,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A440" s="63" t="s">
         <v>81</v>
       </c>
@@ -11180,7 +11181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A441" s="64"/>
       <c r="B441" s="57"/>
       <c r="C441" s="29"/>
@@ -11195,12 +11196,12 @@
         <v>154</v>
       </c>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A443" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A445" s="22" t="s">
         <v>5</v>
       </c>
@@ -11220,7 +11221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A446" s="34">
         <v>0</v>
       </c>
@@ -11240,7 +11241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A447" s="35"/>
       <c r="B447" s="14"/>
       <c r="C447" s="14"/>
@@ -11250,7 +11251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A448" s="34">
         <v>0</v>
       </c>
@@ -11270,7 +11271,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A449" s="35"/>
       <c r="B449" s="14"/>
       <c r="C449" s="16">
@@ -11282,7 +11283,7 @@
       <c r="E449" s="55"/>
       <c r="F449" s="29"/>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A450" s="34">
         <v>0</v>
       </c>
@@ -11302,7 +11303,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A451" s="35"/>
       <c r="B451" s="40">
         <v>0</v>
@@ -11316,7 +11317,7 @@
       </c>
       <c r="F451" s="29"/>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A452" s="34">
         <v>0</v>
       </c>
@@ -11336,7 +11337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A453" s="35"/>
       <c r="B453" s="16">
         <v>40</v>
@@ -11348,7 +11349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A454" s="63">
         <v>0</v>
       </c>
@@ -11368,7 +11369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A455" s="64"/>
       <c r="B455" s="57"/>
       <c r="C455" s="29"/>
@@ -11380,12 +11381,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A457" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A459" s="22"/>
       <c r="B459" s="23" t="s">
         <v>53</v>
@@ -11406,7 +11407,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A460" s="34" t="s">
         <v>23</v>
       </c>
@@ -11429,7 +11430,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A461" s="35"/>
       <c r="B461" s="14"/>
       <c r="C461" s="14"/>
@@ -11442,7 +11443,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A462" s="34" t="s">
         <v>159</v>
       </c>
@@ -11465,7 +11466,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A463" s="35"/>
       <c r="B463" s="14"/>
       <c r="C463" s="16">
@@ -11480,7 +11481,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A464" s="34" t="s">
         <v>160</v>
       </c>
@@ -11503,7 +11504,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A465" s="35"/>
       <c r="B465" s="40">
         <v>0</v>
@@ -11520,7 +11521,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A466" s="34" t="s">
         <v>58</v>
       </c>
@@ -11543,7 +11544,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A467" s="35"/>
       <c r="B467" s="16">
         <v>40</v>
@@ -11558,7 +11559,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A468" s="63" t="s">
         <v>161</v>
       </c>
@@ -11578,7 +11579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A469" s="64"/>
       <c r="B469" s="57"/>
       <c r="C469" s="29"/>
@@ -11590,62 +11591,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A471" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A472" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A474" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A475" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A476" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A477" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A478" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A479" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A480" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A481" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A483" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A485" s="22"/>
       <c r="B485" s="23">
         <v>0</v>
@@ -11661,7 +11662,7 @@
       </c>
       <c r="F485" s="48"/>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A486" s="34">
         <v>0</v>
       </c>
@@ -11679,7 +11680,7 @@
       </c>
       <c r="F486" s="48"/>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A487" s="35"/>
       <c r="B487" s="14"/>
       <c r="C487" s="16">
@@ -11691,7 +11692,7 @@
       </c>
       <c r="F487" s="49"/>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A488" s="34">
         <v>0</v>
       </c>
@@ -11709,7 +11710,7 @@
       </c>
       <c r="F488" s="48"/>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A489" s="35"/>
       <c r="B489" s="14"/>
       <c r="C489" s="16">
@@ -11723,7 +11724,7 @@
       </c>
       <c r="F489" s="48"/>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A490" s="34">
         <v>0</v>
       </c>
@@ -11741,7 +11742,7 @@
       </c>
       <c r="F490" s="48"/>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A491" s="35"/>
       <c r="B491" s="40">
         <v>0</v>
@@ -11755,7 +11756,7 @@
       </c>
       <c r="F491" s="48"/>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A492" s="34">
         <v>0</v>
       </c>
@@ -11773,7 +11774,7 @@
       </c>
       <c r="F492" s="48"/>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A493" s="35"/>
       <c r="B493" s="16">
         <v>40</v>
@@ -11785,7 +11786,7 @@
       </c>
       <c r="F493" s="49"/>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A494" s="52"/>
       <c r="B494" s="48"/>
       <c r="C494" s="48"/>
@@ -11793,7 +11794,7 @@
       <c r="E494" s="48"/>
       <c r="F494" s="48"/>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A495" s="49" t="s">
         <v>175</v>
       </c>
@@ -11803,10 +11804,10 @@
       <c r="E495" s="48"/>
       <c r="F495" s="49"/>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.45">
       <c r="F496" s="70"/>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A497" s="22" t="s">
         <v>5</v>
       </c>
@@ -11842,7 +11843,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A498" s="22">
         <v>40</v>
       </c>
@@ -11875,7 +11876,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A499" s="22">
         <v>50</v>
       </c>
@@ -11908,7 +11909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A500" s="22">
         <v>50</v>
       </c>
@@ -11941,7 +11942,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A501" s="22">
         <v>40</v>
       </c>
@@ -11974,7 +11975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A502" s="44">
         <v>10</v>
       </c>
@@ -12007,7 +12008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.45">
       <c r="G504" s="46" t="s">
         <v>100</v>
       </c>
@@ -12042,19 +12043,119 @@
     </scenario>
   </scenarios>
   <mergeCells count="150">
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A10:XFD10"/>
-    <mergeCell ref="A1:XFD1"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A289:A290"/>
+    <mergeCell ref="A291:A292"/>
+    <mergeCell ref="A293:A294"/>
+    <mergeCell ref="A295:A296"/>
+    <mergeCell ref="A297:A298"/>
+    <mergeCell ref="AQ275:AQ276"/>
+    <mergeCell ref="AQ277:AQ278"/>
+    <mergeCell ref="AQ279:AQ280"/>
+    <mergeCell ref="AQ281:AQ282"/>
+    <mergeCell ref="AQ283:AQ284"/>
+    <mergeCell ref="O275:O276"/>
+    <mergeCell ref="O277:O278"/>
+    <mergeCell ref="O279:O280"/>
+    <mergeCell ref="O281:O282"/>
+    <mergeCell ref="O283:O284"/>
+    <mergeCell ref="V275:V276"/>
+    <mergeCell ref="V277:V278"/>
+    <mergeCell ref="V279:V280"/>
+    <mergeCell ref="V281:V282"/>
+    <mergeCell ref="V283:V284"/>
+    <mergeCell ref="A277:A278"/>
+    <mergeCell ref="A279:A280"/>
+    <mergeCell ref="A281:A282"/>
+    <mergeCell ref="A283:A284"/>
+    <mergeCell ref="AX275:AX276"/>
+    <mergeCell ref="AX277:AX278"/>
+    <mergeCell ref="AX279:AX280"/>
+    <mergeCell ref="AX281:AX282"/>
+    <mergeCell ref="AX283:AX284"/>
+    <mergeCell ref="AC275:AC276"/>
+    <mergeCell ref="AC277:AC278"/>
+    <mergeCell ref="AC279:AC280"/>
+    <mergeCell ref="AC281:AC282"/>
+    <mergeCell ref="AC283:AC284"/>
+    <mergeCell ref="AJ275:AJ276"/>
+    <mergeCell ref="AJ277:AJ278"/>
+    <mergeCell ref="AJ279:AJ280"/>
+    <mergeCell ref="AJ281:AJ282"/>
+    <mergeCell ref="AJ283:AJ284"/>
+    <mergeCell ref="H275:H276"/>
+    <mergeCell ref="H277:H278"/>
+    <mergeCell ref="H279:H280"/>
+    <mergeCell ref="H281:H282"/>
+    <mergeCell ref="H283:H284"/>
+    <mergeCell ref="A265:A266"/>
+    <mergeCell ref="A267:A268"/>
+    <mergeCell ref="A269:A270"/>
+    <mergeCell ref="A271:A272"/>
+    <mergeCell ref="A275:A276"/>
+    <mergeCell ref="A260:XFD260"/>
+    <mergeCell ref="A234:A235"/>
+    <mergeCell ref="A218:A219"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="A228:A229"/>
+    <mergeCell ref="A230:A231"/>
+    <mergeCell ref="A232:A233"/>
+    <mergeCell ref="A202:A203"/>
+    <mergeCell ref="A204:A205"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="A214:A215"/>
+    <mergeCell ref="A216:A217"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A192:A193"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="A200:A201"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="AE27:AE28"/>
+    <mergeCell ref="AE29:AE30"/>
+    <mergeCell ref="AE31:AE32"/>
+    <mergeCell ref="AE33:AE34"/>
+    <mergeCell ref="AE35:AE36"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="M27:M28"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="M33:M34"/>
+    <mergeCell ref="M35:M36"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="A49:A50"/>
     <mergeCell ref="A20:XFD20"/>
@@ -12079,119 +12180,19 @@
     <mergeCell ref="Y31:Y32"/>
     <mergeCell ref="Y33:Y34"/>
     <mergeCell ref="Y35:Y36"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="AE27:AE28"/>
-    <mergeCell ref="AE29:AE30"/>
-    <mergeCell ref="AE31:AE32"/>
-    <mergeCell ref="AE33:AE34"/>
-    <mergeCell ref="AE35:AE36"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="M27:M28"/>
-    <mergeCell ref="M29:M30"/>
-    <mergeCell ref="M31:M32"/>
-    <mergeCell ref="M33:M34"/>
-    <mergeCell ref="M35:M36"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A192:A193"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="A200:A201"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="A260:XFD260"/>
-    <mergeCell ref="A234:A235"/>
-    <mergeCell ref="A218:A219"/>
-    <mergeCell ref="A220:A221"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="A228:A229"/>
-    <mergeCell ref="A230:A231"/>
-    <mergeCell ref="A232:A233"/>
-    <mergeCell ref="A202:A203"/>
-    <mergeCell ref="A204:A205"/>
-    <mergeCell ref="A206:A207"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="A214:A215"/>
-    <mergeCell ref="A216:A217"/>
-    <mergeCell ref="H275:H276"/>
-    <mergeCell ref="H277:H278"/>
-    <mergeCell ref="H279:H280"/>
-    <mergeCell ref="H281:H282"/>
-    <mergeCell ref="H283:H284"/>
-    <mergeCell ref="A265:A266"/>
-    <mergeCell ref="A267:A268"/>
-    <mergeCell ref="A269:A270"/>
-    <mergeCell ref="A271:A272"/>
-    <mergeCell ref="A275:A276"/>
-    <mergeCell ref="AX275:AX276"/>
-    <mergeCell ref="AX277:AX278"/>
-    <mergeCell ref="AX279:AX280"/>
-    <mergeCell ref="AX281:AX282"/>
-    <mergeCell ref="AX283:AX284"/>
-    <mergeCell ref="AC275:AC276"/>
-    <mergeCell ref="AC277:AC278"/>
-    <mergeCell ref="AC279:AC280"/>
-    <mergeCell ref="AC281:AC282"/>
-    <mergeCell ref="AC283:AC284"/>
-    <mergeCell ref="AJ275:AJ276"/>
-    <mergeCell ref="AJ277:AJ278"/>
-    <mergeCell ref="AJ279:AJ280"/>
-    <mergeCell ref="AJ281:AJ282"/>
-    <mergeCell ref="AJ283:AJ284"/>
-    <mergeCell ref="A289:A290"/>
-    <mergeCell ref="A291:A292"/>
-    <mergeCell ref="A293:A294"/>
-    <mergeCell ref="A295:A296"/>
-    <mergeCell ref="A297:A298"/>
-    <mergeCell ref="AQ275:AQ276"/>
-    <mergeCell ref="AQ277:AQ278"/>
-    <mergeCell ref="AQ279:AQ280"/>
-    <mergeCell ref="AQ281:AQ282"/>
-    <mergeCell ref="AQ283:AQ284"/>
-    <mergeCell ref="O275:O276"/>
-    <mergeCell ref="O277:O278"/>
-    <mergeCell ref="O279:O280"/>
-    <mergeCell ref="O281:O282"/>
-    <mergeCell ref="O283:O284"/>
-    <mergeCell ref="V275:V276"/>
-    <mergeCell ref="V277:V278"/>
-    <mergeCell ref="V279:V280"/>
-    <mergeCell ref="V281:V282"/>
-    <mergeCell ref="V283:V284"/>
-    <mergeCell ref="A277:A278"/>
-    <mergeCell ref="A279:A280"/>
-    <mergeCell ref="A281:A282"/>
-    <mergeCell ref="A283:A284"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A10:XFD10"/>
+    <mergeCell ref="A1:XFD1"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="H5:J5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -12202,28 +12203,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDDA934F-B0A8-40A8-B6B4-830AD47FDEE9}">
   <dimension ref="A1:AV180"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="15.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="47"/>
+    <col min="1" max="16384" width="8.90625" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="118" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="118" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" s="101" customFormat="1" x14ac:dyDescent="0.4"/>
-    <row r="13" spans="1:11" s="118" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="118" t="s">
+    <row r="1" spans="1:11" s="116" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="116" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="101" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="13" spans="1:11" s="116" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="116" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="D15" s="47" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="D16" s="47" t="s">
         <v>255</v>
       </c>
@@ -12234,7 +12235,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="D17" s="47" t="s">
         <v>256</v>
       </c>
@@ -12245,7 +12246,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="D18" s="47" t="s">
         <v>257</v>
       </c>
@@ -12253,12 +12254,12 @@
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K19" s="47" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="D20" s="47" t="s">
         <v>178</v>
       </c>
@@ -12269,23 +12270,23 @@
         <v>180</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="125" t="s">
+    <row r="23" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="124" t="s">
         <v>191</v>
       </c>
-      <c r="B23" s="125"/>
-      <c r="C23" s="125"/>
-      <c r="D23" s="125"/>
-      <c r="F23" s="125" t="s">
+      <c r="B23" s="124"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="124"/>
+      <c r="F23" s="124" t="s">
         <v>192</v>
       </c>
-      <c r="G23" s="125"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="125"/>
-      <c r="K23" s="125"/>
-    </row>
-    <row r="24" spans="1:11" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G23" s="124"/>
+      <c r="H23" s="124"/>
+      <c r="I23" s="124"/>
+      <c r="J23" s="124"/>
+      <c r="K23" s="124"/>
+    </row>
+    <row r="24" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A24" s="89"/>
       <c r="B24" s="90" t="s">
         <v>183</v>
@@ -12309,7 +12310,7 @@
       </c>
       <c r="K24" s="92"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" s="87" t="s">
         <v>181</v>
       </c>
@@ -12341,7 +12342,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A26" s="85" t="s">
         <v>182</v>
       </c>
@@ -12373,7 +12374,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A27" s="85" t="s">
         <v>185</v>
       </c>
@@ -12401,7 +12402,7 @@
       </c>
       <c r="K27" s="81"/>
     </row>
-    <row r="28" spans="1:11" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A28" s="86"/>
       <c r="B28" s="97">
         <v>350</v>
@@ -12411,13 +12412,13 @@
       </c>
       <c r="D28" s="81"/>
     </row>
-    <row r="30" spans="1:11" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A30" s="47" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="16.8" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="32" spans="1:11" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="32" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A32" s="89"/>
       <c r="B32" s="90" t="s">
         <v>183</v>
@@ -12438,7 +12439,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" s="87" t="s">
         <v>181</v>
       </c>
@@ -12461,7 +12462,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" s="85" t="s">
         <v>182</v>
       </c>
@@ -12484,7 +12485,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A35" s="86" t="s">
         <v>185</v>
       </c>
@@ -12507,7 +12508,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" s="84" t="s">
         <v>183</v>
       </c>
@@ -12530,7 +12531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A37" s="86" t="s">
         <v>184</v>
       </c>
@@ -12553,13 +12554,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A39" s="47" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="41" spans="1:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="41" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A41" s="89"/>
       <c r="B41" s="90" t="s">
         <v>183</v>
@@ -12584,7 +12585,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" s="87" t="s">
         <v>181</v>
       </c>
@@ -12614,7 +12615,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" s="85" t="s">
         <v>182</v>
       </c>
@@ -12644,7 +12645,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A44" s="86" t="s">
         <v>185</v>
       </c>
@@ -12674,7 +12675,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45" s="84" t="s">
         <v>183</v>
       </c>
@@ -12704,7 +12705,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A46" s="86" t="s">
         <v>184</v>
       </c>
@@ -12734,7 +12735,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B47" s="47">
         <f>SUM(B42:B46)</f>
         <v>350</v>
@@ -12760,7 +12761,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48" s="47">
         <f>SUM(B48:G48)</f>
         <v>1390</v>
@@ -12788,15 +12789,15 @@
         <v>11580</v>
       </c>
     </row>
-    <row r="50" spans="1:23" s="118" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="118" t="s">
+    <row r="50" spans="1:23" s="116" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="116" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A51"/>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A52" s="22"/>
       <c r="B52" s="23">
         <v>350</v>
@@ -12841,7 +12842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A53" s="99">
         <v>340</v>
       </c>
@@ -12898,7 +12899,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A54" s="100"/>
       <c r="B54" s="20"/>
       <c r="C54" s="20"/>
@@ -12929,7 +12930,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A55" s="99">
         <v>150</v>
       </c>
@@ -12986,7 +12987,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A56" s="100"/>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
@@ -13015,7 +13016,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A57" s="99">
         <v>100</v>
       </c>
@@ -13072,7 +13073,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A58" s="100"/>
       <c r="B58" s="58"/>
       <c r="C58" s="58"/>
@@ -13103,7 +13104,7 @@
       </c>
       <c r="W58" s="39"/>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A59" s="99">
         <v>210</v>
       </c>
@@ -13160,7 +13161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A60" s="100"/>
       <c r="B60" s="20"/>
       <c r="C60" s="20"/>
@@ -13183,12 +13184,12 @@
         <v>210</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A62" s="47" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A64" s="22" t="s">
         <v>5</v>
       </c>
@@ -13199,7 +13200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" s="99">
         <v>0</v>
       </c>
@@ -13210,7 +13211,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="100"/>
       <c r="B66" s="16">
         <v>250</v>
@@ -13219,7 +13220,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" s="99">
         <v>0</v>
       </c>
@@ -13230,14 +13231,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="100"/>
       <c r="B68" s="14"/>
       <c r="C68" s="16">
         <v>150</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69" s="99">
         <v>0</v>
       </c>
@@ -13248,14 +13249,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="100"/>
       <c r="B70" s="40">
         <v>100</v>
       </c>
       <c r="C70" s="39"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="99">
         <v>0</v>
       </c>
@@ -13266,29 +13267,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="100"/>
       <c r="B72" s="14"/>
       <c r="C72" s="16">
         <v>210</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="47" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="47" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="47" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="22"/>
       <c r="B79" s="23" t="s">
         <v>204</v>
@@ -13300,7 +13301,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="99" t="s">
         <v>23</v>
       </c>
@@ -13314,7 +13315,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="81" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A81" s="100"/>
       <c r="B81" s="16">
         <v>250</v>
@@ -13326,7 +13327,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="82" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A82" s="99" t="s">
         <v>56</v>
       </c>
@@ -13340,7 +13341,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="83" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A83" s="100"/>
       <c r="B83" s="14"/>
       <c r="C83" s="16">
@@ -13350,7 +13351,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="84" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A84" s="99" t="s">
         <v>206</v>
       </c>
@@ -13361,14 +13362,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A85" s="100"/>
       <c r="B85" s="40">
         <v>100</v>
       </c>
       <c r="C85" s="39"/>
     </row>
-    <row r="86" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A86" s="99" t="s">
         <v>207</v>
       </c>
@@ -13379,44 +13380,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A87" s="100"/>
       <c r="B87" s="14"/>
       <c r="C87" s="16">
         <v>210</v>
       </c>
     </row>
-    <row r="89" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A89" s="47" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="90" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A90" s="47" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="91" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A91" s="47" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A92" s="47" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="93" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A93" s="47" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="94" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A94" s="47" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="96" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A96" s="22" t="s">
         <v>5</v>
       </c>
@@ -13544,8 +13545,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:48" x14ac:dyDescent="0.4">
-      <c r="A97" s="114">
+    <row r="97" spans="1:48" x14ac:dyDescent="0.45">
+      <c r="A97" s="118">
         <v>350</v>
       </c>
       <c r="B97" s="8">
@@ -13563,7 +13564,7 @@
       <c r="F97" s="106">
         <v>0</v>
       </c>
-      <c r="H97" s="114">
+      <c r="H97" s="118">
         <v>250</v>
       </c>
       <c r="I97" s="8">
@@ -13581,7 +13582,7 @@
       <c r="M97" s="106">
         <v>0</v>
       </c>
-      <c r="O97" s="114">
+      <c r="O97" s="118">
         <v>120</v>
       </c>
       <c r="P97" s="8">
@@ -13599,7 +13600,7 @@
       <c r="T97" s="106">
         <v>0</v>
       </c>
-      <c r="V97" s="114">
+      <c r="V97" s="118">
         <v>0</v>
       </c>
       <c r="W97" s="13">
@@ -13617,7 +13618,7 @@
       <c r="AA97" s="108">
         <v>0</v>
       </c>
-      <c r="AC97" s="114">
+      <c r="AC97" s="118">
         <v>0</v>
       </c>
       <c r="AD97" s="13">
@@ -13635,7 +13636,7 @@
       <c r="AH97" s="108">
         <v>0</v>
       </c>
-      <c r="AJ97" s="114">
+      <c r="AJ97" s="118">
         <v>0</v>
       </c>
       <c r="AK97" s="13">
@@ -13653,7 +13654,7 @@
       <c r="AO97" s="108">
         <v>0</v>
       </c>
-      <c r="AQ97" s="114">
+      <c r="AQ97" s="118">
         <v>0</v>
       </c>
       <c r="AR97" s="13">
@@ -13672,14 +13673,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:48" x14ac:dyDescent="0.4">
-      <c r="A98" s="115"/>
+    <row r="98" spans="1:48" x14ac:dyDescent="0.45">
+      <c r="A98" s="119"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
       <c r="D98" s="12"/>
       <c r="E98" s="12"/>
       <c r="F98" s="104"/>
-      <c r="H98" s="115"/>
+      <c r="H98" s="119"/>
       <c r="I98" s="12"/>
       <c r="J98" s="12"/>
       <c r="K98" s="12"/>
@@ -13687,7 +13688,7 @@
         <v>100</v>
       </c>
       <c r="M98" s="104"/>
-      <c r="O98" s="115"/>
+      <c r="O98" s="119"/>
       <c r="P98" s="12"/>
       <c r="Q98" s="12"/>
       <c r="R98" s="16">
@@ -13697,7 +13698,7 @@
         <v>100</v>
       </c>
       <c r="T98" s="104"/>
-      <c r="V98" s="115"/>
+      <c r="V98" s="119"/>
       <c r="W98" s="14"/>
       <c r="X98" s="16">
         <v>120</v>
@@ -13709,7 +13710,7 @@
         <v>100</v>
       </c>
       <c r="AA98" s="109"/>
-      <c r="AC98" s="115"/>
+      <c r="AC98" s="119"/>
       <c r="AD98" s="14"/>
       <c r="AE98" s="16">
         <v>120</v>
@@ -13721,7 +13722,7 @@
         <v>100</v>
       </c>
       <c r="AH98" s="109"/>
-      <c r="AJ98" s="115"/>
+      <c r="AJ98" s="119"/>
       <c r="AK98" s="14"/>
       <c r="AL98" s="16">
         <v>120</v>
@@ -13733,7 +13734,7 @@
         <v>100</v>
       </c>
       <c r="AO98" s="109"/>
-      <c r="AQ98" s="115"/>
+      <c r="AQ98" s="119"/>
       <c r="AR98" s="14"/>
       <c r="AS98" s="16">
         <v>120</v>
@@ -13746,8 +13747,8 @@
       </c>
       <c r="AV98" s="109"/>
     </row>
-    <row r="99" spans="1:48" x14ac:dyDescent="0.4">
-      <c r="A99" s="114">
+    <row r="99" spans="1:48" x14ac:dyDescent="0.45">
+      <c r="A99" s="118">
         <v>450</v>
       </c>
       <c r="B99" s="8">
@@ -13765,7 +13766,7 @@
       <c r="F99" s="107">
         <v>0</v>
       </c>
-      <c r="H99" s="114">
+      <c r="H99" s="118">
         <v>450</v>
       </c>
       <c r="I99" s="8">
@@ -13783,7 +13784,7 @@
       <c r="M99" s="107">
         <v>0</v>
       </c>
-      <c r="O99" s="114">
+      <c r="O99" s="118">
         <v>450</v>
       </c>
       <c r="P99" s="8">
@@ -13801,7 +13802,7 @@
       <c r="T99" s="107">
         <v>0</v>
       </c>
-      <c r="V99" s="114">
+      <c r="V99" s="118">
         <v>450</v>
       </c>
       <c r="W99" s="8">
@@ -13819,7 +13820,7 @@
       <c r="AA99" s="107">
         <v>0</v>
       </c>
-      <c r="AC99" s="114">
+      <c r="AC99" s="118">
         <v>410</v>
       </c>
       <c r="AD99" s="8">
@@ -13837,7 +13838,7 @@
       <c r="AH99" s="107">
         <v>0</v>
       </c>
-      <c r="AJ99" s="114">
+      <c r="AJ99" s="118">
         <v>210</v>
       </c>
       <c r="AK99" s="15">
@@ -13855,7 +13856,7 @@
       <c r="AO99" s="107">
         <v>0</v>
       </c>
-      <c r="AQ99" s="114">
+      <c r="AQ99" s="118">
         <v>0</v>
       </c>
       <c r="AR99" s="15">
@@ -13874,32 +13875,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:48" x14ac:dyDescent="0.4">
-      <c r="A100" s="115"/>
+    <row r="100" spans="1:48" x14ac:dyDescent="0.45">
+      <c r="A100" s="119"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
       <c r="D100" s="12"/>
       <c r="E100" s="12"/>
       <c r="F100" s="104"/>
-      <c r="H100" s="115"/>
+      <c r="H100" s="119"/>
       <c r="I100" s="12"/>
       <c r="J100" s="12"/>
       <c r="K100" s="12"/>
       <c r="L100" s="14"/>
       <c r="M100" s="104"/>
-      <c r="O100" s="115"/>
+      <c r="O100" s="119"/>
       <c r="P100" s="12"/>
       <c r="Q100" s="12"/>
       <c r="R100" s="14"/>
       <c r="S100" s="14"/>
       <c r="T100" s="104"/>
-      <c r="V100" s="115"/>
+      <c r="V100" s="119"/>
       <c r="W100" s="12"/>
       <c r="X100" s="12"/>
       <c r="Y100" s="14"/>
       <c r="Z100" s="14"/>
       <c r="AA100" s="104"/>
-      <c r="AC100" s="115"/>
+      <c r="AC100" s="119"/>
       <c r="AD100" s="12"/>
       <c r="AE100" s="16">
         <v>40</v>
@@ -13907,7 +13908,7 @@
       <c r="AF100" s="14"/>
       <c r="AG100" s="14"/>
       <c r="AH100" s="104"/>
-      <c r="AJ100" s="115"/>
+      <c r="AJ100" s="119"/>
       <c r="AK100" s="16">
         <v>200</v>
       </c>
@@ -13917,7 +13918,7 @@
       <c r="AM100" s="14"/>
       <c r="AN100" s="14"/>
       <c r="AO100" s="104"/>
-      <c r="AQ100" s="115"/>
+      <c r="AQ100" s="119"/>
       <c r="AR100" s="16">
         <v>200</v>
       </c>
@@ -13930,14 +13931,14 @@
         <v>210</v>
       </c>
     </row>
-    <row r="101" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A101" s="27"/>
       <c r="B101" s="102"/>
       <c r="C101" s="102"/>
       <c r="D101" s="102"/>
       <c r="E101" s="102"/>
     </row>
-    <row r="102" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A102" s="112" t="s">
         <v>42</v>
       </c>
@@ -13946,14 +13947,14 @@
       <c r="D102" s="102"/>
       <c r="E102" s="102"/>
     </row>
-    <row r="103" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A103" s="27"/>
       <c r="B103" s="49"/>
       <c r="C103" s="49"/>
       <c r="D103" s="49"/>
       <c r="E103" s="49"/>
     </row>
-    <row r="104" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A104" s="22" t="s">
         <v>5</v>
       </c>
@@ -13973,8 +13974,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:48" x14ac:dyDescent="0.4">
-      <c r="A105" s="114">
+    <row r="105" spans="1:48" x14ac:dyDescent="0.45">
+      <c r="A105" s="118">
         <v>0</v>
       </c>
       <c r="B105" s="13">
@@ -13993,8 +13994,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:48" x14ac:dyDescent="0.4">
-      <c r="A106" s="115"/>
+    <row r="106" spans="1:48" x14ac:dyDescent="0.45">
+      <c r="A106" s="119"/>
       <c r="B106" s="14"/>
       <c r="C106" s="16">
         <v>120</v>
@@ -14007,8 +14008,8 @@
       </c>
       <c r="F106" s="109"/>
     </row>
-    <row r="107" spans="1:48" x14ac:dyDescent="0.4">
-      <c r="A107" s="114">
+    <row r="107" spans="1:48" x14ac:dyDescent="0.45">
+      <c r="A107" s="118">
         <v>0</v>
       </c>
       <c r="B107" s="15">
@@ -14027,8 +14028,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:48" x14ac:dyDescent="0.4">
-      <c r="A108" s="115"/>
+    <row r="108" spans="1:48" x14ac:dyDescent="0.45">
+      <c r="A108" s="119"/>
       <c r="B108" s="16">
         <v>200</v>
       </c>
@@ -14041,22 +14042,22 @@
         <v>210</v>
       </c>
     </row>
-    <row r="110" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A110" s="47" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="111" spans="1:48" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A111" s="47" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113" s="47" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115" s="22"/>
       <c r="B115" s="23" t="s">
         <v>220</v>
@@ -14077,8 +14078,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A116" s="114" t="s">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A116" s="118" t="s">
         <v>23</v>
       </c>
       <c r="B116" s="13">
@@ -14100,8 +14101,8 @@
         <v>215</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A117" s="115"/>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A117" s="119"/>
       <c r="B117" s="14"/>
       <c r="C117" s="16">
         <v>120</v>
@@ -14117,8 +14118,8 @@
         <v>216</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A118" s="114" t="s">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A118" s="118" t="s">
         <v>223</v>
       </c>
       <c r="B118" s="15">
@@ -14140,8 +14141,8 @@
         <v>217</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A119" s="115"/>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A119" s="119"/>
       <c r="B119" s="16">
         <v>200</v>
       </c>
@@ -14157,17 +14158,17 @@
         <v>218</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
       <c r="H120" s="47" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" s="47" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" s="22" t="s">
         <v>5</v>
       </c>
@@ -14187,8 +14188,8 @@
         <v>222</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A124" s="114" t="s">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A124" s="118" t="s">
         <v>23</v>
       </c>
       <c r="B124" s="13">
@@ -14207,8 +14208,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A125" s="115"/>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A125" s="119"/>
       <c r="B125" s="14"/>
       <c r="C125" s="16" t="s">
         <v>227</v>
@@ -14221,8 +14222,8 @@
       </c>
       <c r="F125" s="109"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A126" s="114" t="s">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A126" s="118" t="s">
         <v>223</v>
       </c>
       <c r="B126" s="15">
@@ -14241,8 +14242,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A127" s="115"/>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A127" s="119"/>
       <c r="B127" s="16">
         <v>200</v>
       </c>
@@ -14260,12 +14261,12 @@
         <v>228</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" s="47" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131" s="22" t="s">
         <v>5</v>
       </c>
@@ -14285,8 +14286,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A132" s="114">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A132" s="118">
         <v>0</v>
       </c>
       <c r="B132" s="13">
@@ -14305,8 +14306,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A133" s="115"/>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A133" s="119"/>
       <c r="B133" s="14"/>
       <c r="C133" s="16">
         <v>160</v>
@@ -14319,8 +14320,8 @@
       </c>
       <c r="F133" s="109"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A134" s="114">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A134" s="118">
         <v>0</v>
       </c>
       <c r="B134" s="15">
@@ -14339,8 +14340,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A135" s="115"/>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A135" s="119"/>
       <c r="B135" s="16">
         <v>200</v>
       </c>
@@ -14353,12 +14354,12 @@
         <v>210</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" s="47" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" s="22"/>
       <c r="B139" s="23" t="s">
         <v>232</v>
@@ -14379,8 +14380,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A140" s="114" t="s">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A140" s="118" t="s">
         <v>23</v>
       </c>
       <c r="B140" s="13">
@@ -14402,8 +14403,8 @@
         <v>218</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A141" s="115"/>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A141" s="119"/>
       <c r="B141" s="14"/>
       <c r="C141" s="16">
         <v>160</v>
@@ -14419,8 +14420,8 @@
         <v>219</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A142" s="114" t="s">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A142" s="118" t="s">
         <v>159</v>
       </c>
       <c r="B142" s="15">
@@ -14442,8 +14443,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A143" s="115"/>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A143" s="119"/>
       <c r="B143" s="16">
         <v>200</v>
       </c>
@@ -14459,17 +14460,17 @@
         <v>230</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="H144" s="47" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A145" s="47" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A147" s="22"/>
       <c r="B147" s="23" t="s">
         <v>232</v>
@@ -14487,8 +14488,8 @@
         <v>142</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A148" s="114" t="s">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A148" s="118" t="s">
         <v>23</v>
       </c>
       <c r="B148" s="13">
@@ -14507,8 +14508,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A149" s="115"/>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A149" s="119"/>
       <c r="B149" s="14" t="s">
         <v>82</v>
       </c>
@@ -14523,8 +14524,8 @@
       </c>
       <c r="F149" s="109"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A150" s="114" t="s">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A150" s="118" t="s">
         <v>159</v>
       </c>
       <c r="B150" s="15">
@@ -14543,8 +14544,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A151" s="115"/>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A151" s="119"/>
       <c r="B151" s="16" t="s">
         <v>235</v>
       </c>
@@ -14560,12 +14561,12 @@
         <v>236</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A153" s="47" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A155" s="22" t="s">
         <v>5</v>
       </c>
@@ -14585,8 +14586,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A156" s="114">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A156" s="118">
         <v>0</v>
       </c>
       <c r="B156" s="15">
@@ -14605,8 +14606,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A157" s="115"/>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A157" s="119"/>
       <c r="B157" s="16">
         <v>60</v>
       </c>
@@ -14619,8 +14620,8 @@
       <c r="E157" s="14"/>
       <c r="F157" s="109"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A158" s="114">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A158" s="118">
         <v>0</v>
       </c>
       <c r="B158" s="15">
@@ -14639,8 +14640,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A159" s="115"/>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A159" s="119"/>
       <c r="B159" s="16">
         <v>140</v>
       </c>
@@ -14653,12 +14654,12 @@
         <v>210</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A161" s="47" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A163" s="22"/>
       <c r="B163" s="23" t="s">
         <v>220</v>
@@ -14679,8 +14680,8 @@
         <v>237</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A164" s="114" t="s">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A164" s="118" t="s">
         <v>23</v>
       </c>
       <c r="B164" s="15">
@@ -14702,8 +14703,8 @@
         <v>238</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A165" s="115"/>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A165" s="119"/>
       <c r="B165" s="16">
         <v>60</v>
       </c>
@@ -14719,8 +14720,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A166" s="114" t="s">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A166" s="118" t="s">
         <v>223</v>
       </c>
       <c r="B166" s="15">
@@ -14742,8 +14743,8 @@
         <v>217</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A167" s="115"/>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A167" s="119"/>
       <c r="B167" s="16">
         <v>140</v>
       </c>
@@ -14759,96 +14760,96 @@
         <v>214</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.45">
       <c r="H168" s="47" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A169" s="47" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A170" s="47" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A171" s="47" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A172" s="47" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A173" s="47" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A174" s="47" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="124" t="s">
+    <row r="176" spans="1:11" ht="16.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A176" s="125" t="s">
         <v>244</v>
       </c>
-      <c r="B176" s="124"/>
-      <c r="C176" s="124"/>
-      <c r="D176" s="124"/>
-      <c r="E176" s="124"/>
-      <c r="F176" s="124"/>
-      <c r="G176" s="124"/>
-      <c r="H176" s="124"/>
-      <c r="I176" s="124"/>
-      <c r="J176" s="124"/>
+      <c r="B176" s="125"/>
+      <c r="C176" s="125"/>
+      <c r="D176" s="125"/>
+      <c r="E176" s="125"/>
+      <c r="F176" s="125"/>
+      <c r="G176" s="125"/>
+      <c r="H176" s="125"/>
+      <c r="I176" s="125"/>
+      <c r="J176" s="125"/>
       <c r="K176" s="113"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A177" s="124"/>
-      <c r="B177" s="124"/>
-      <c r="C177" s="124"/>
-      <c r="D177" s="124"/>
-      <c r="E177" s="124"/>
-      <c r="F177" s="124"/>
-      <c r="G177" s="124"/>
-      <c r="H177" s="124"/>
-      <c r="I177" s="124"/>
-      <c r="J177" s="124"/>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A177" s="125"/>
+      <c r="B177" s="125"/>
+      <c r="C177" s="125"/>
+      <c r="D177" s="125"/>
+      <c r="E177" s="125"/>
+      <c r="F177" s="125"/>
+      <c r="G177" s="125"/>
+      <c r="H177" s="125"/>
+      <c r="I177" s="125"/>
+      <c r="J177" s="125"/>
       <c r="K177" s="113"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A178" s="124"/>
-      <c r="B178" s="124"/>
-      <c r="C178" s="124"/>
-      <c r="D178" s="124"/>
-      <c r="E178" s="124"/>
-      <c r="F178" s="124"/>
-      <c r="G178" s="124"/>
-      <c r="H178" s="124"/>
-      <c r="I178" s="124"/>
-      <c r="J178" s="124"/>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A178" s="125"/>
+      <c r="B178" s="125"/>
+      <c r="C178" s="125"/>
+      <c r="D178" s="125"/>
+      <c r="E178" s="125"/>
+      <c r="F178" s="125"/>
+      <c r="G178" s="125"/>
+      <c r="H178" s="125"/>
+      <c r="I178" s="125"/>
+      <c r="J178" s="125"/>
       <c r="K178" s="113"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A179" s="124"/>
-      <c r="B179" s="124"/>
-      <c r="C179" s="124"/>
-      <c r="D179" s="124"/>
-      <c r="E179" s="124"/>
-      <c r="F179" s="124"/>
-      <c r="G179" s="124"/>
-      <c r="H179" s="124"/>
-      <c r="I179" s="124"/>
-      <c r="J179" s="124"/>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A179" s="125"/>
+      <c r="B179" s="125"/>
+      <c r="C179" s="125"/>
+      <c r="D179" s="125"/>
+      <c r="E179" s="125"/>
+      <c r="F179" s="125"/>
+      <c r="G179" s="125"/>
+      <c r="H179" s="125"/>
+      <c r="I179" s="125"/>
+      <c r="J179" s="125"/>
       <c r="K179" s="113"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A180" s="113"/>
       <c r="B180" s="113"/>
       <c r="C180" s="113"/>
@@ -14863,11 +14864,22 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A1:XFD1"/>
-    <mergeCell ref="A13:XFD13"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="F23:K23"/>
-    <mergeCell ref="A50:XFD50"/>
+    <mergeCell ref="A176:J179"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A107:A108"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A127"/>
     <mergeCell ref="AJ97:AJ98"/>
     <mergeCell ref="AJ99:AJ100"/>
     <mergeCell ref="AQ97:AQ98"/>
@@ -14883,22 +14895,11 @@
     <mergeCell ref="V99:V100"/>
     <mergeCell ref="AC97:AC98"/>
     <mergeCell ref="AC99:AC100"/>
-    <mergeCell ref="A107:A108"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A176:J179"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A1:XFD1"/>
+    <mergeCell ref="A13:XFD13"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F23:K23"/>
+    <mergeCell ref="A50:XFD50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
